--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>25355</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>79.4000015258789</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>82.9000015258789</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>81.9000015258789</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>10944</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>84</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>80.5999984741211</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>82.0999984741211</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>80.5999984741211</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>24326</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>86.3000030517578</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>82</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>82.5999984741211</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>86</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>6398</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>87.9000015258789</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>86</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>87</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>86.1999969482422</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>8157</v>
+        <v>5307</v>
       </c>
       <c r="C2715" t="n">
-        <v>85.9000015258789</v>
+        <v>85.8000030517578</v>
       </c>
       <c r="D2715" t="n">
         <v>83.9000015258789</v>
       </c>
       <c r="E2715" t="n">
-        <v>85.9000015258789</v>
+        <v>84</v>
       </c>
       <c r="F2715" t="n">
-        <v>84.3000030517578</v>
+        <v>85</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>5327</v>
+        <v>8157</v>
       </c>
       <c r="C2716" t="n">
-        <v>84</v>
+        <v>85.9000015258789</v>
       </c>
       <c r="D2716" t="n">
-        <v>81.3000030517578</v>
+        <v>83.9000015258789</v>
       </c>
       <c r="E2716" t="n">
-        <v>83.6999969482422</v>
+        <v>85.9000015258789</v>
       </c>
       <c r="F2716" t="n">
-        <v>81.8000030517578</v>
+        <v>84.3000030517578</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,19 +62842,19 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>6528</v>
+        <v>5327</v>
       </c>
       <c r="C2717" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2717" t="n">
-        <v>80.8000030517578</v>
+        <v>81.3000030517578</v>
       </c>
       <c r="E2717" t="n">
-        <v>81.5</v>
+        <v>83.6999969482422</v>
       </c>
       <c r="F2717" t="n">
         <v>81.8000030517578</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>39326</v>
+        <v>6528</v>
       </c>
       <c r="C2718" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D2718" t="n">
-        <v>80.9000015258789</v>
+        <v>80.8000030517578</v>
       </c>
       <c r="E2718" t="n">
-        <v>82</v>
+        <v>81.5</v>
       </c>
       <c r="F2718" t="n">
-        <v>82.5999984741211</v>
+        <v>81.8000030517578</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>25355</v>
+        <v>39326</v>
       </c>
       <c r="C2719" t="n">
-        <v>84.5</v>
+        <v>89</v>
       </c>
       <c r="D2719" t="n">
-        <v>79.4000015258789</v>
+        <v>80.9000015258789</v>
       </c>
       <c r="E2719" t="n">
-        <v>82.9000015258789</v>
+        <v>82</v>
       </c>
       <c r="F2719" t="n">
-        <v>81.9000015258789</v>
+        <v>82.5999984741211</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>10944</v>
+        <v>25355</v>
       </c>
       <c r="C2720" t="n">
-        <v>84</v>
+        <v>84.5</v>
       </c>
       <c r="D2720" t="n">
-        <v>80.5999984741211</v>
+        <v>79.4000015258789</v>
       </c>
       <c r="E2720" t="n">
-        <v>82.0999984741211</v>
+        <v>82.9000015258789</v>
       </c>
       <c r="F2720" t="n">
-        <v>80.5999984741211</v>
+        <v>81.9000015258789</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>24326</v>
+        <v>10944</v>
       </c>
       <c r="C2721" t="n">
-        <v>86.3000030517578</v>
+        <v>84</v>
       </c>
       <c r="D2721" t="n">
-        <v>82</v>
+        <v>80.5999984741211</v>
       </c>
       <c r="E2721" t="n">
-        <v>82.5999984741211</v>
+        <v>82.0999984741211</v>
       </c>
       <c r="F2721" t="n">
-        <v>86</v>
+        <v>80.5999984741211</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>6398</v>
+        <v>24326</v>
       </c>
       <c r="C2722" t="n">
-        <v>87.9000015258789</v>
+        <v>86.3000030517578</v>
       </c>
       <c r="D2722" t="n">
+        <v>82</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>82.5999984741211</v>
+      </c>
+      <c r="F2722" t="n">
         <v>86</v>
       </c>
-      <c r="E2722" t="n">
-        <v>87</v>
-      </c>
-      <c r="F2722" t="n">
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>14526</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>88.3000030517578</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>85.3000030517578</v>
+      </c>
+      <c r="E2723" t="n">
         <v>86.1999969482422</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>85</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>83.9000015258789</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>85</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>10367</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>88</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>84.6999969482422</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>85.3000030517578</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>85.3000030517578</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>87.5</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>11264</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>89.0999984741211</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>85.9000015258789</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -63305,7 +63305,7 @@
         <v>46302.2916666667</v>
       </c>
       <c r="B2737" t="n">
-        <v>11264</v>
+        <v>11346</v>
       </c>
       <c r="C2737" t="n">
         <v>89.0999984741211</v>
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>88</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>87.3000030517578</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>10346</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>87.9000015258789</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>84</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>86.3000030517578</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>86.3000030517578</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>84.3000030517578</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>5214</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>85.5999984741211</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>85.5999984741211</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>7142</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>86.3000030517578</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>83.0999984741211</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>83.0999984741211</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>84.3000030517578</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>9.04536819458008</v>
+        <v>9.04536724090576</v>
       </c>
       <c r="H2" t="n">
         <v>5120</v>
@@ -456,7 +456,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G3" t="n">
-        <v>9.35568428039551</v>
+        <v>9.35568332672119</v>
       </c>
       <c r="H3" t="n">
         <v>14550</v>
@@ -485,7 +485,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G4" t="n">
-        <v>9.11799621582031</v>
+        <v>9.11799430847168</v>
       </c>
       <c r="H4" t="n">
         <v>1924</v>
@@ -659,7 +659,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G10" t="n">
-        <v>9.16421222686768</v>
+        <v>9.16421318054199</v>
       </c>
       <c r="H10" t="n">
         <v>5726</v>
@@ -688,7 +688,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G11" t="n">
-        <v>9.11799621582031</v>
+        <v>9.11799430847168</v>
       </c>
       <c r="H11" t="n">
         <v>15279</v>
@@ -746,7 +746,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G13" t="n">
-        <v>9.12459754943848</v>
+        <v>9.12459850311279</v>
       </c>
       <c r="H13" t="n">
         <v>1260</v>
@@ -775,7 +775,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G14" t="n">
-        <v>9.07177829742432</v>
+        <v>9.07177734375</v>
       </c>
       <c r="H14" t="n">
         <v>5420</v>
@@ -833,7 +833,7 @@
         <v>13.75</v>
       </c>
       <c r="G16" t="n">
-        <v>9.0783805847168</v>
+        <v>9.07838153839111</v>
       </c>
       <c r="H16" t="n">
         <v>4800</v>
@@ -891,7 +891,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G18" t="n">
-        <v>9.07177829742432</v>
+        <v>9.07177734375</v>
       </c>
       <c r="H18" t="n">
         <v>6463</v>
@@ -920,7 +920,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G19" t="n">
-        <v>9.00575351715088</v>
+        <v>9.0057544708252</v>
       </c>
       <c r="H19" t="n">
         <v>1236</v>
@@ -978,7 +978,7 @@
         <v>13.75</v>
       </c>
       <c r="G21" t="n">
-        <v>9.0783805847168</v>
+        <v>9.07838153839111</v>
       </c>
       <c r="H21" t="n">
         <v>1646</v>
@@ -1007,7 +1007,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G22" t="n">
-        <v>9.00575351715088</v>
+        <v>9.0057544708252</v>
       </c>
       <c r="H22" t="n">
         <v>1401</v>
@@ -1036,7 +1036,7 @@
         <v>13.5</v>
       </c>
       <c r="G23" t="n">
-        <v>8.9133186340332</v>
+        <v>8.91331958770752</v>
       </c>
       <c r="H23" t="n">
         <v>1906</v>
@@ -1065,7 +1065,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G24" t="n">
-        <v>8.65582275390625</v>
+        <v>8.65582370758057</v>
       </c>
       <c r="H24" t="n">
         <v>3762</v>
@@ -1094,7 +1094,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>8.5897970199585</v>
+        <v>8.58979797363281</v>
       </c>
       <c r="H25" t="n">
         <v>2451</v>
@@ -1123,7 +1123,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>8.66242599487305</v>
+        <v>8.66242504119873</v>
       </c>
       <c r="H26" t="n">
         <v>1794</v>
@@ -1210,7 +1210,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>8.43794345855713</v>
+        <v>8.4379415512085</v>
       </c>
       <c r="H29" t="n">
         <v>3639</v>
@@ -1239,7 +1239,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>8.2728796005249</v>
+        <v>8.27288150787354</v>
       </c>
       <c r="H30" t="n">
         <v>895</v>
@@ -1268,7 +1268,7 @@
         <v>12.5</v>
       </c>
       <c r="G31" t="n">
-        <v>8.25307369232178</v>
+        <v>8.25307464599609</v>
       </c>
       <c r="H31" t="n">
         <v>1135</v>
@@ -1297,7 +1297,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>8.45114707946777</v>
+        <v>8.45114612579346</v>
       </c>
       <c r="H32" t="n">
         <v>3280</v>
@@ -1413,7 +1413,7 @@
         <v>13.5</v>
       </c>
       <c r="G36" t="n">
-        <v>8.9133186340332</v>
+        <v>8.91331958770752</v>
       </c>
       <c r="H36" t="n">
         <v>3330</v>
@@ -1442,7 +1442,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G37" t="n">
-        <v>8.8803071975708</v>
+        <v>8.88030815124512</v>
       </c>
       <c r="H37" t="n">
         <v>3428</v>
@@ -1471,7 +1471,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>8.68883323669434</v>
+        <v>8.68883609771729</v>
       </c>
       <c r="H38" t="n">
         <v>1813</v>
@@ -1500,7 +1500,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>8.78126907348633</v>
+        <v>8.78127002716064</v>
       </c>
       <c r="H39" t="n">
         <v>318</v>
@@ -1529,7 +1529,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>8.78126907348633</v>
+        <v>8.78127002716064</v>
       </c>
       <c r="H40" t="n">
         <v>2404</v>
@@ -1587,7 +1587,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G42" t="n">
-        <v>8.45114707946777</v>
+        <v>8.45114612579346</v>
       </c>
       <c r="H42" t="n">
         <v>6024</v>
@@ -1616,7 +1616,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>8.48415946960449</v>
+        <v>8.48415851593018</v>
       </c>
       <c r="H43" t="n">
         <v>2917</v>
@@ -1674,7 +1674,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G45" t="n">
-        <v>8.62941360473633</v>
+        <v>8.62941265106201</v>
       </c>
       <c r="H45" t="n">
         <v>418</v>
@@ -1790,7 +1790,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G49" t="n">
-        <v>8.78787136077881</v>
+        <v>8.78787326812744</v>
       </c>
       <c r="H49" t="n">
         <v>1452</v>
@@ -1819,7 +1819,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G50" t="n">
-        <v>9.00575351715088</v>
+        <v>9.0057544708252</v>
       </c>
       <c r="H50" t="n">
         <v>3270</v>
@@ -1848,7 +1848,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>8.99254703521729</v>
+        <v>8.9925479888916</v>
       </c>
       <c r="H51" t="n">
         <v>7650</v>
@@ -1935,7 +1935,7 @@
         <v>13.5</v>
       </c>
       <c r="G54" t="n">
-        <v>8.9133186340332</v>
+        <v>8.91331958770752</v>
       </c>
       <c r="H54" t="n">
         <v>1531</v>
@@ -1993,7 +1993,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G56" t="n">
-        <v>9.1510066986084</v>
+        <v>9.15100765228271</v>
       </c>
       <c r="H56" t="n">
         <v>7727</v>
@@ -2022,7 +2022,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G57" t="n">
-        <v>9.1510066986084</v>
+        <v>9.15100765228271</v>
       </c>
       <c r="H57" t="n">
         <v>2799</v>
@@ -2051,7 +2051,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>9.04536819458008</v>
+        <v>9.04536724090576</v>
       </c>
       <c r="H58" t="n">
         <v>2800</v>
@@ -2080,7 +2080,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>9.04536819458008</v>
+        <v>9.04536724090576</v>
       </c>
       <c r="H59" t="n">
         <v>3967</v>
@@ -2109,7 +2109,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G60" t="n">
-        <v>9.05857181549072</v>
+        <v>9.05857276916504</v>
       </c>
       <c r="H60" t="n">
         <v>2378</v>
@@ -2167,7 +2167,7 @@
         <v>13.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.9133186340332</v>
+        <v>8.91331958770752</v>
       </c>
       <c r="H62" t="n">
         <v>2188</v>
@@ -2283,7 +2283,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G66" t="n">
-        <v>8.60300445556641</v>
+        <v>8.60300254821777</v>
       </c>
       <c r="H66" t="n">
         <v>2010</v>
@@ -2341,7 +2341,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G68" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312740325928</v>
       </c>
       <c r="H68" t="n">
         <v>4443</v>
@@ -2370,7 +2370,7 @@
         <v>13.5</v>
       </c>
       <c r="G69" t="n">
-        <v>8.9133186340332</v>
+        <v>8.91331958770752</v>
       </c>
       <c r="H69" t="n">
         <v>221</v>
@@ -2399,7 +2399,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>8.84729385375977</v>
+        <v>8.84729290008545</v>
       </c>
       <c r="H70" t="n">
         <v>131</v>
@@ -2457,7 +2457,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G72" t="n">
-        <v>8.99254703521729</v>
+        <v>8.9925479888916</v>
       </c>
       <c r="H72" t="n">
         <v>1300</v>
@@ -2486,7 +2486,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G73" t="n">
-        <v>9.01895904541016</v>
+        <v>9.01895713806152</v>
       </c>
       <c r="H73" t="n">
         <v>1659</v>
@@ -2515,7 +2515,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G74" t="n">
-        <v>8.85389614105225</v>
+        <v>8.85389518737793</v>
       </c>
       <c r="H74" t="n">
         <v>263</v>
@@ -2544,7 +2544,7 @@
         <v>13.5</v>
       </c>
       <c r="G75" t="n">
-        <v>8.9133186340332</v>
+        <v>8.91331958770752</v>
       </c>
       <c r="H75" t="n">
         <v>890</v>
@@ -2573,7 +2573,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G76" t="n">
-        <v>8.90671730041504</v>
+        <v>8.90671634674072</v>
       </c>
       <c r="H76" t="n">
         <v>4550</v>
@@ -2660,7 +2660,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>9.04536819458008</v>
+        <v>9.04536724090576</v>
       </c>
       <c r="H79" t="n">
         <v>4163</v>
@@ -2689,7 +2689,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>9.01235485076904</v>
+        <v>9.01235675811768</v>
       </c>
       <c r="H80" t="n">
         <v>359</v>
@@ -2747,7 +2747,7 @@
         <v>13.5</v>
       </c>
       <c r="G82" t="n">
-        <v>8.9133186340332</v>
+        <v>8.91331958770752</v>
       </c>
       <c r="H82" t="n">
         <v>2266</v>
@@ -2805,7 +2805,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>9.00575351715088</v>
+        <v>9.0057544708252</v>
       </c>
       <c r="H84" t="n">
         <v>1046</v>
@@ -2834,7 +2834,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>9.1840181350708</v>
+        <v>9.18401908874512</v>
       </c>
       <c r="H85" t="n">
         <v>2238</v>
@@ -2892,7 +2892,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G87" t="n">
-        <v>9.09158420562744</v>
+        <v>9.09158515930176</v>
       </c>
       <c r="H87" t="n">
         <v>750</v>
@@ -2921,7 +2921,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>9.01235485076904</v>
+        <v>9.01235675811768</v>
       </c>
       <c r="H88" t="n">
         <v>704</v>
@@ -2950,7 +2950,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G89" t="n">
-        <v>8.99254703521729</v>
+        <v>8.9925479888916</v>
       </c>
       <c r="H89" t="n">
         <v>3</v>
@@ -2979,7 +2979,7 @@
         <v>13.5</v>
       </c>
       <c r="G90" t="n">
-        <v>8.9133186340332</v>
+        <v>8.91331958770752</v>
       </c>
       <c r="H90" t="n">
         <v>2182</v>
@@ -3008,7 +3008,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G91" t="n">
-        <v>9.01235485076904</v>
+        <v>9.01235675811768</v>
       </c>
       <c r="H91" t="n">
         <v>5042</v>
@@ -3037,7 +3037,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>8.8803071975708</v>
+        <v>8.88030815124512</v>
       </c>
       <c r="H92" t="n">
         <v>202</v>
@@ -3066,7 +3066,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G93" t="n">
-        <v>8.84729385375977</v>
+        <v>8.84729290008545</v>
       </c>
       <c r="H93" t="n">
         <v>4992</v>
@@ -3124,7 +3124,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G95" t="n">
-        <v>9.02717876434326</v>
+        <v>9.02717971801758</v>
       </c>
       <c r="H95" t="n">
         <v>8454</v>
@@ -3153,7 +3153,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G96" t="n">
-        <v>9.03401184082031</v>
+        <v>9.03401279449463</v>
       </c>
       <c r="H96" t="n">
         <v>1439</v>
@@ -3211,7 +3211,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H98" t="n">
         <v>17761</v>
@@ -3240,7 +3240,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H99" t="n">
         <v>5743</v>
@@ -3269,7 +3269,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G100" t="n">
-        <v>9.21168518066406</v>
+        <v>9.21168613433838</v>
       </c>
       <c r="H100" t="n">
         <v>2702</v>
@@ -3298,7 +3298,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G101" t="n">
-        <v>9.32102298736572</v>
+        <v>9.32102394104004</v>
       </c>
       <c r="H101" t="n">
         <v>9051</v>
@@ -3327,7 +3327,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G102" t="n">
-        <v>9.2936897277832</v>
+        <v>9.29368877410889</v>
       </c>
       <c r="H102" t="n">
         <v>8510</v>
@@ -3472,7 +3472,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>9.46452903747559</v>
+        <v>9.46452808380127</v>
       </c>
       <c r="H107" t="n">
         <v>16441</v>
@@ -3559,7 +3559,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G110" t="n">
-        <v>9.36885929107666</v>
+        <v>9.36885833740234</v>
       </c>
       <c r="H110" t="n">
         <v>3764</v>
@@ -3675,7 +3675,7 @@
         <v>13.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.22535228729248</v>
+        <v>9.22535419464111</v>
       </c>
       <c r="H114" t="n">
         <v>13372</v>
@@ -3704,7 +3704,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G115" t="n">
-        <v>9.19801902770996</v>
+        <v>9.19801998138428</v>
       </c>
       <c r="H115" t="n">
         <v>8947</v>
@@ -3733,7 +3733,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G116" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H116" t="n">
         <v>4769</v>
@@ -3791,7 +3791,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G118" t="n">
-        <v>9.15018272399902</v>
+        <v>9.15018367767334</v>
       </c>
       <c r="H118" t="n">
         <v>575</v>
@@ -3849,7 +3849,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G120" t="n">
-        <v>9.42352867126465</v>
+        <v>9.42352771759033</v>
       </c>
       <c r="H120" t="n">
         <v>13694</v>
@@ -3965,7 +3965,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H124" t="n">
         <v>4885</v>
@@ -3994,7 +3994,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G125" t="n">
-        <v>9.03401184082031</v>
+        <v>9.03401279449463</v>
       </c>
       <c r="H125" t="n">
         <v>4429</v>
@@ -4081,7 +4081,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G128" t="n">
-        <v>9.36885929107666</v>
+        <v>9.36885833740234</v>
       </c>
       <c r="H128" t="n">
         <v>1325</v>
@@ -4110,7 +4110,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G129" t="n">
-        <v>9.36202526092529</v>
+        <v>9.36202430725098</v>
       </c>
       <c r="H129" t="n">
         <v>387</v>
@@ -4168,7 +4168,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.36202526092529</v>
+        <v>9.36202430725098</v>
       </c>
       <c r="H131" t="n">
         <v>863</v>
@@ -4226,7 +4226,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G133" t="n">
-        <v>9.33469009399414</v>
+        <v>9.33468914031982</v>
       </c>
       <c r="H133" t="n">
         <v>800</v>
@@ -4284,7 +4284,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H135" t="n">
         <v>1110</v>
@@ -4313,7 +4313,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H136" t="n">
         <v>6831</v>
@@ -4342,7 +4342,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H138" t="n">
         <v>2959</v>
@@ -4400,7 +4400,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G139" t="n">
-        <v>8.93150901794434</v>
+        <v>8.93150806427002</v>
       </c>
       <c r="H139" t="n">
         <v>11518</v>
@@ -4487,7 +4487,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H142" t="n">
         <v>1543</v>
@@ -4516,7 +4516,7 @@
         <v>13.5</v>
       </c>
       <c r="G143" t="n">
-        <v>9.22535228729248</v>
+        <v>9.22535419464111</v>
       </c>
       <c r="H143" t="n">
         <v>223</v>
@@ -4545,7 +4545,7 @@
         <v>13.5</v>
       </c>
       <c r="G144" t="n">
-        <v>9.22535228729248</v>
+        <v>9.22535419464111</v>
       </c>
       <c r="H144" t="n">
         <v>12524</v>
@@ -4574,7 +4574,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H145" t="n">
         <v>577</v>
@@ -4603,7 +4603,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>9.08868026733398</v>
+        <v>9.0886812210083</v>
       </c>
       <c r="H146" t="n">
         <v>356</v>
@@ -4661,7 +4661,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H148" t="n">
         <v>3847</v>
@@ -4719,7 +4719,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G150" t="n">
-        <v>9.08184623718262</v>
+        <v>9.08184719085693</v>
       </c>
       <c r="H150" t="n">
         <v>1606</v>
@@ -4835,7 +4835,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G154" t="n">
-        <v>9.09551429748535</v>
+        <v>9.09551620483398</v>
       </c>
       <c r="H154" t="n">
         <v>1975</v>
@@ -4864,7 +4864,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G155" t="n">
-        <v>9.1023473739624</v>
+        <v>9.10234832763672</v>
       </c>
       <c r="H155" t="n">
         <v>759</v>
@@ -5009,7 +5009,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G160" t="n">
-        <v>9.17068481445312</v>
+        <v>9.17068386077881</v>
       </c>
       <c r="H160" t="n">
         <v>312</v>
@@ -5067,7 +5067,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G162" t="n">
-        <v>9.27318859100342</v>
+        <v>9.2731876373291</v>
       </c>
       <c r="H162" t="n">
         <v>182</v>
@@ -5096,7 +5096,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.32785606384277</v>
+        <v>9.32785797119141</v>
       </c>
       <c r="H163" t="n">
         <v>540</v>
@@ -5125,7 +5125,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G164" t="n">
-        <v>9.3073558807373</v>
+        <v>9.30735683441162</v>
       </c>
       <c r="H164" t="n">
         <v>6349</v>
@@ -5183,7 +5183,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>9.2936897277832</v>
+        <v>9.29368877410889</v>
       </c>
       <c r="H166" t="n">
         <v>160</v>
@@ -5212,7 +5212,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>9.2936897277832</v>
+        <v>9.29368877410889</v>
       </c>
       <c r="H167" t="n">
         <v>688</v>
@@ -5241,7 +5241,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G168" t="n">
-        <v>9.2936897277832</v>
+        <v>9.29368877410889</v>
       </c>
       <c r="H168" t="n">
         <v>1185</v>
@@ -5270,7 +5270,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G169" t="n">
-        <v>9.2936897277832</v>
+        <v>9.29368877410889</v>
       </c>
       <c r="H169" t="n">
         <v>998</v>
@@ -5357,7 +5357,7 @@
         <v>13.5</v>
       </c>
       <c r="G172" t="n">
-        <v>9.22535228729248</v>
+        <v>9.22535419464111</v>
       </c>
       <c r="H172" t="n">
         <v>9485</v>
@@ -5386,7 +5386,7 @@
         <v>13.5</v>
       </c>
       <c r="G173" t="n">
-        <v>9.22535228729248</v>
+        <v>9.22535419464111</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>9.32785606384277</v>
+        <v>9.32785797119141</v>
       </c>
       <c r="H174" t="n">
         <v>1822</v>
@@ -5444,7 +5444,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G175" t="n">
-        <v>9.32102298736572</v>
+        <v>9.32102394104004</v>
       </c>
       <c r="H175" t="n">
         <v>1057</v>
@@ -5531,7 +5531,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G178" t="n">
-        <v>9.21168518066406</v>
+        <v>9.21168613433838</v>
       </c>
       <c r="H178" t="n">
         <v>1700</v>
@@ -5560,7 +5560,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G179" t="n">
-        <v>9.12968158721924</v>
+        <v>9.12968254089355</v>
       </c>
       <c r="H179" t="n">
         <v>363</v>
@@ -5618,7 +5618,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>8.95201015472412</v>
+        <v>8.95200824737549</v>
       </c>
       <c r="H181" t="n">
         <v>3399</v>
@@ -5647,7 +5647,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G182" t="n">
-        <v>8.95884323120117</v>
+        <v>8.95884418487549</v>
       </c>
       <c r="H182" t="n">
         <v>5884</v>
@@ -5734,7 +5734,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G185" t="n">
-        <v>8.8495044708252</v>
+        <v>8.84950351715088</v>
       </c>
       <c r="H185" t="n">
         <v>3986</v>
@@ -5763,7 +5763,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G186" t="n">
-        <v>8.74016857147217</v>
+        <v>8.74016761779785</v>
       </c>
       <c r="H186" t="n">
         <v>10826</v>
@@ -5821,7 +5821,7 @@
         <v>13</v>
       </c>
       <c r="G188" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H188" t="n">
         <v>17597</v>
@@ -5850,7 +5850,7 @@
         <v>13</v>
       </c>
       <c r="G189" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H189" t="n">
         <v>460</v>
@@ -5879,7 +5879,7 @@
         <v>13</v>
       </c>
       <c r="G190" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H190" t="n">
         <v>626</v>
@@ -5908,7 +5908,7 @@
         <v>13</v>
       </c>
       <c r="G191" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H191" t="n">
         <v>17871</v>
@@ -5937,7 +5937,7 @@
         <v>13</v>
       </c>
       <c r="G192" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H192" t="n">
         <v>2541</v>
@@ -5966,7 +5966,7 @@
         <v>13</v>
       </c>
       <c r="G193" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H193" t="n">
         <v>3614</v>
@@ -5995,7 +5995,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G194" t="n">
-        <v>8.78800296783447</v>
+        <v>8.78800201416016</v>
       </c>
       <c r="H194" t="n">
         <v>2036</v>
@@ -6053,7 +6053,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G196" t="n">
-        <v>8.66499710083008</v>
+        <v>8.66499900817871</v>
       </c>
       <c r="H196" t="n">
         <v>19703</v>
@@ -6111,7 +6111,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G198" t="n">
-        <v>8.73333549499512</v>
+        <v>8.73333358764648</v>
       </c>
       <c r="H198" t="n">
         <v>561</v>
@@ -6140,7 +6140,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G199" t="n">
-        <v>8.76750183105469</v>
+        <v>8.76750087738037</v>
       </c>
       <c r="H199" t="n">
         <v>1580</v>
@@ -6169,7 +6169,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>8.78116989135742</v>
+        <v>8.78116893768311</v>
       </c>
       <c r="H200" t="n">
         <v>13369</v>
@@ -6198,7 +6198,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>8.78116989135742</v>
+        <v>8.78116893768311</v>
       </c>
       <c r="H201" t="n">
         <v>1203</v>
@@ -6227,7 +6227,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G202" t="n">
-        <v>8.8495044708252</v>
+        <v>8.84950351715088</v>
       </c>
       <c r="H202" t="n">
         <v>12953</v>
@@ -6343,7 +6343,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G206" t="n">
-        <v>8.69233131408691</v>
+        <v>8.69233226776123</v>
       </c>
       <c r="H206" t="n">
         <v>2314</v>
@@ -6430,7 +6430,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G209" t="n">
-        <v>8.38482093811035</v>
+        <v>8.38481998443604</v>
       </c>
       <c r="H209" t="n">
         <v>4921</v>
@@ -6459,7 +6459,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G210" t="n">
-        <v>8.63083076477051</v>
+        <v>8.63082885742188</v>
       </c>
       <c r="H210" t="n">
         <v>53127</v>
@@ -6488,7 +6488,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G211" t="n">
-        <v>8.63083076477051</v>
+        <v>8.63082885742188</v>
       </c>
       <c r="H211" t="n">
         <v>12117</v>
@@ -6546,7 +6546,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G213" t="n">
-        <v>8.66499710083008</v>
+        <v>8.66499900817871</v>
       </c>
       <c r="H213" t="n">
         <v>8955</v>
@@ -6662,7 +6662,7 @@
         <v>12.75</v>
       </c>
       <c r="G217" t="n">
-        <v>8.7128324508667</v>
+        <v>8.71283340454102</v>
       </c>
       <c r="H217" t="n">
         <v>4155</v>
@@ -6720,7 +6720,7 @@
         <v>13</v>
       </c>
       <c r="G219" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H219" t="n">
         <v>1319</v>
@@ -6807,7 +6807,7 @@
         <v>13</v>
       </c>
       <c r="G222" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H222" t="n">
         <v>975</v>
@@ -6923,7 +6923,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G226" t="n">
-        <v>8.77433681488037</v>
+        <v>8.77433490753174</v>
       </c>
       <c r="H226" t="n">
         <v>2795</v>
@@ -6952,7 +6952,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H227" t="n">
         <v>9485</v>
@@ -7010,7 +7010,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G229" t="n">
-        <v>8.89734172821045</v>
+        <v>8.89734077453613</v>
       </c>
       <c r="H229" t="n">
         <v>1149</v>
@@ -7097,7 +7097,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G232" t="n">
-        <v>8.85633945465088</v>
+        <v>8.85633850097656</v>
       </c>
       <c r="H232" t="n">
         <v>1649</v>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H233" t="n">
         <v>461</v>
@@ -7155,7 +7155,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>8.95201015472412</v>
+        <v>8.95200824737549</v>
       </c>
       <c r="H234" t="n">
         <v>966</v>
@@ -7184,7 +7184,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>8.8495044708252</v>
+        <v>8.84950351715088</v>
       </c>
       <c r="H235" t="n">
         <v>15524</v>
@@ -7213,7 +7213,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H236" t="n">
         <v>4265</v>
@@ -7242,7 +7242,7 @@
         <v>13</v>
       </c>
       <c r="G237" t="n">
-        <v>8.88367462158203</v>
+        <v>8.88367366790771</v>
       </c>
       <c r="H237" t="n">
         <v>1142</v>
@@ -7271,7 +7271,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G238" t="n">
-        <v>8.9041748046875</v>
+        <v>8.90417385101318</v>
       </c>
       <c r="H238" t="n">
         <v>2580</v>
@@ -7300,7 +7300,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>8.8495044708252</v>
+        <v>8.84950351715088</v>
       </c>
       <c r="H239" t="n">
         <v>3706</v>
@@ -7329,7 +7329,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G240" t="n">
-        <v>9.21168518066406</v>
+        <v>9.21168613433838</v>
       </c>
       <c r="H240" t="n">
         <v>18137</v>
@@ -7358,7 +7358,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G241" t="n">
-        <v>9.21168518066406</v>
+        <v>9.21168613433838</v>
       </c>
       <c r="H241" t="n">
         <v>7100</v>
@@ -7416,7 +7416,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H243" t="n">
         <v>4970</v>
@@ -7445,7 +7445,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>9.15701675415039</v>
+        <v>9.15701580047607</v>
       </c>
       <c r="H244" t="n">
         <v>3427</v>
@@ -7474,7 +7474,7 @@
         <v>13.5</v>
       </c>
       <c r="G245" t="n">
-        <v>9.22535228729248</v>
+        <v>9.22535419464111</v>
       </c>
       <c r="H245" t="n">
         <v>5876</v>
@@ -7503,7 +7503,7 @@
         <v>13.5</v>
       </c>
       <c r="G246" t="n">
-        <v>9.22535228729248</v>
+        <v>9.22535419464111</v>
       </c>
       <c r="H246" t="n">
         <v>9737</v>
@@ -7532,7 +7532,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>9.2936897277832</v>
+        <v>9.29368877410889</v>
       </c>
       <c r="H247" t="n">
         <v>12587</v>
@@ -7677,7 +7677,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.36202526092529</v>
+        <v>9.36202430725098</v>
       </c>
       <c r="H252" t="n">
         <v>3408</v>
@@ -7706,7 +7706,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G253" t="n">
-        <v>9.45769500732422</v>
+        <v>9.4576940536499</v>
       </c>
       <c r="H253" t="n">
         <v>1434</v>
@@ -7735,7 +7735,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G254" t="n">
-        <v>9.45769500732422</v>
+        <v>9.4576940536499</v>
       </c>
       <c r="H254" t="n">
         <v>2076</v>
@@ -7764,7 +7764,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G255" t="n">
-        <v>9.4440279006958</v>
+        <v>9.44402885437012</v>
       </c>
       <c r="H255" t="n">
         <v>1028</v>
@@ -7793,7 +7793,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>9.3073558807373</v>
+        <v>9.30735683441162</v>
       </c>
       <c r="H256" t="n">
         <v>2149</v>
@@ -7880,7 +7880,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G259" t="n">
-        <v>9.58753395080566</v>
+        <v>9.58753299713135</v>
       </c>
       <c r="H259" t="n">
         <v>17367</v>
@@ -7909,7 +7909,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G260" t="n">
-        <v>9.71737289428711</v>
+        <v>9.71737194061279</v>
       </c>
       <c r="H260" t="n">
         <v>6568</v>
@@ -7938,7 +7938,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G261" t="n">
-        <v>9.77204036712646</v>
+        <v>9.77204132080078</v>
       </c>
       <c r="H261" t="n">
         <v>6024</v>
@@ -7967,7 +7967,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>9.84037590026855</v>
+        <v>9.84037494659424</v>
       </c>
       <c r="H262" t="n">
         <v>1127</v>
@@ -7996,7 +7996,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>9.84037590026855</v>
+        <v>9.84037494659424</v>
       </c>
       <c r="H263" t="n">
         <v>6087</v>
@@ -8025,7 +8025,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G264" t="n">
-        <v>10.1957235336304</v>
+        <v>10.1957244873047</v>
       </c>
       <c r="H264" t="n">
         <v>8120</v>
@@ -8083,7 +8083,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G266" t="n">
-        <v>10.0317182540894</v>
+        <v>10.0317163467407</v>
       </c>
       <c r="H266" t="n">
         <v>2591</v>
@@ -8112,7 +8112,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G267" t="n">
-        <v>9.93604755401611</v>
+        <v>9.9360466003418</v>
       </c>
       <c r="H267" t="n">
         <v>6664</v>
@@ -8141,7 +8141,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G268" t="n">
-        <v>9.93604755401611</v>
+        <v>9.9360466003418</v>
       </c>
       <c r="H268" t="n">
         <v>3847</v>
@@ -8199,7 +8199,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G270" t="n">
-        <v>10.0522193908691</v>
+        <v>10.0522174835205</v>
       </c>
       <c r="H270" t="n">
         <v>11668</v>
@@ -8257,7 +8257,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G272" t="n">
-        <v>10.1752243041992</v>
+        <v>10.1752233505249</v>
       </c>
       <c r="H272" t="n">
         <v>15309</v>
@@ -8286,7 +8286,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G273" t="n">
-        <v>10.3187284469604</v>
+        <v>10.3187294006348</v>
       </c>
       <c r="H273" t="n">
         <v>17702</v>
@@ -8344,7 +8344,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G275" t="n">
-        <v>10.2640600204468</v>
+        <v>10.2640590667725</v>
       </c>
       <c r="H275" t="n">
         <v>7075</v>
@@ -8402,7 +8402,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G277" t="n">
-        <v>10.1410541534424</v>
+        <v>10.1410551071167</v>
       </c>
       <c r="H277" t="n">
         <v>6951</v>
@@ -8489,7 +8489,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>9.84037590026855</v>
+        <v>9.84037494659424</v>
       </c>
       <c r="H280" t="n">
         <v>5403</v>
@@ -8605,7 +8605,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G284" t="n">
-        <v>10.1683902740479</v>
+        <v>10.1683883666992</v>
       </c>
       <c r="H284" t="n">
         <v>12237</v>
@@ -8779,7 +8779,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>10.1820573806763</v>
+        <v>10.182056427002</v>
       </c>
       <c r="H290" t="n">
         <v>9199</v>
@@ -8808,7 +8808,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>10.2162246704102</v>
+        <v>10.2162237167358</v>
       </c>
       <c r="H291" t="n">
         <v>3407</v>
@@ -8837,7 +8837,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G292" t="n">
-        <v>10.1547222137451</v>
+        <v>10.1547212600708</v>
       </c>
       <c r="H292" t="n">
         <v>2255</v>
@@ -8895,7 +8895,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.1478891372681</v>
+        <v>10.1478872299194</v>
       </c>
       <c r="H294" t="n">
         <v>4012</v>
@@ -8924,7 +8924,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G295" t="n">
-        <v>10.1820573806763</v>
+        <v>10.182056427002</v>
       </c>
       <c r="H295" t="n">
         <v>4152</v>
@@ -8953,7 +8953,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G296" t="n">
-        <v>10.1205558776855</v>
+        <v>10.1205539703369</v>
       </c>
       <c r="H296" t="n">
         <v>5516</v>
@@ -9011,7 +9011,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>10.1820573806763</v>
+        <v>10.182056427002</v>
       </c>
       <c r="H298" t="n">
         <v>1053</v>
@@ -9040,7 +9040,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G299" t="n">
-        <v>10.1752243041992</v>
+        <v>10.1752233505249</v>
       </c>
       <c r="H299" t="n">
         <v>3502</v>
@@ -9069,7 +9069,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G300" t="n">
-        <v>10.1752243041992</v>
+        <v>10.1752233505249</v>
       </c>
       <c r="H300" t="n">
         <v>3974</v>
@@ -9098,7 +9098,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G301" t="n">
-        <v>10.0658845901489</v>
+        <v>10.0658855438232</v>
       </c>
       <c r="H301" t="n">
         <v>5565</v>
@@ -9127,7 +9127,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G302" t="n">
-        <v>10.1820573806763</v>
+        <v>10.182056427002</v>
       </c>
       <c r="H302" t="n">
         <v>4682</v>
@@ -9156,7 +9156,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>10.1478891372681</v>
+        <v>10.1478872299194</v>
       </c>
       <c r="H303" t="n">
         <v>1297</v>
@@ -9185,7 +9185,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G304" t="n">
-        <v>10.1820573806763</v>
+        <v>10.182056427002</v>
       </c>
       <c r="H304" t="n">
         <v>4949</v>
@@ -9214,7 +9214,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G305" t="n">
-        <v>10.1752243041992</v>
+        <v>10.1752233505249</v>
       </c>
       <c r="H305" t="n">
         <v>2151</v>
@@ -9359,7 +9359,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G310" t="n">
-        <v>10.4690685272217</v>
+        <v>10.4690675735474</v>
       </c>
       <c r="H310" t="n">
         <v>13002</v>
@@ -9475,7 +9475,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>10.8312473297119</v>
+        <v>10.8312463760376</v>
       </c>
       <c r="H314" t="n">
         <v>9856</v>
@@ -9504,7 +9504,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G315" t="n">
-        <v>10.8517484664917</v>
+        <v>10.851749420166</v>
       </c>
       <c r="H315" t="n">
         <v>17227</v>
@@ -9533,7 +9533,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G316" t="n">
-        <v>11.1182584762573</v>
+        <v>11.1182594299316</v>
       </c>
       <c r="H316" t="n">
         <v>33465</v>
@@ -9678,7 +9678,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G321" t="n">
-        <v>11.8494539260864</v>
+        <v>11.8494529724121</v>
       </c>
       <c r="H321" t="n">
         <v>22320</v>
@@ -9707,7 +9707,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G322" t="n">
-        <v>12.0271272659302</v>
+        <v>12.0271263122559</v>
       </c>
       <c r="H322" t="n">
         <v>25667</v>
@@ -9823,7 +9823,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G326" t="n">
-        <v>12.9701623916626</v>
+        <v>12.9701614379883</v>
       </c>
       <c r="H326" t="n">
         <v>53211</v>
@@ -9852,7 +9852,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G327" t="n">
-        <v>12.8334932327271</v>
+        <v>12.8334913253784</v>
       </c>
       <c r="H327" t="n">
         <v>10806</v>
@@ -9881,7 +9881,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G328" t="n">
-        <v>12.8471555709839</v>
+        <v>12.8471593856812</v>
       </c>
       <c r="H328" t="n">
         <v>34067</v>
@@ -9910,7 +9910,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G329" t="n">
-        <v>12.6216506958008</v>
+        <v>12.6216497421265</v>
       </c>
       <c r="H329" t="n">
         <v>16367</v>
@@ -9939,7 +9939,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G330" t="n">
-        <v>12.8471555709839</v>
+        <v>12.8471593856812</v>
       </c>
       <c r="H330" t="n">
         <v>16535</v>
@@ -9968,7 +9968,7 @@
         <v>18.5</v>
       </c>
       <c r="G331" t="n">
-        <v>12.6421508789062</v>
+        <v>12.6421489715576</v>
       </c>
       <c r="H331" t="n">
         <v>12757</v>
@@ -9997,7 +9997,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>12.5738134384155</v>
+        <v>12.5738153457642</v>
       </c>
       <c r="H332" t="n">
         <v>9059</v>
@@ -10055,7 +10055,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>12.9154930114746</v>
+        <v>12.9154920578003</v>
       </c>
       <c r="H334" t="n">
         <v>33384</v>
@@ -10084,7 +10084,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G335" t="n">
-        <v>13.1136684417725</v>
+        <v>13.1136665344238</v>
       </c>
       <c r="H335" t="n">
         <v>79828</v>
@@ -10113,7 +10113,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G336" t="n">
-        <v>13.6056890487671</v>
+        <v>13.6056900024414</v>
       </c>
       <c r="H336" t="n">
         <v>23051</v>
@@ -10142,7 +10142,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G337" t="n">
-        <v>13.6876926422119</v>
+        <v>13.6876916885376</v>
       </c>
       <c r="H337" t="n">
         <v>32064</v>
@@ -10171,7 +10171,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G338" t="n">
-        <v>13.6398553848267</v>
+        <v>13.639853477478</v>
       </c>
       <c r="H338" t="n">
         <v>29392</v>
@@ -10200,7 +10200,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G339" t="n">
-        <v>13.7286911010742</v>
+        <v>13.7286920547485</v>
       </c>
       <c r="H339" t="n">
         <v>19731</v>
@@ -10229,7 +10229,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>13.7355270385742</v>
+        <v>13.7355251312256</v>
       </c>
       <c r="H340" t="n">
         <v>18593</v>
@@ -10258,7 +10258,7 @@
         <v>20.25</v>
       </c>
       <c r="G341" t="n">
-        <v>13.8380308151245</v>
+        <v>13.8380289077759</v>
       </c>
       <c r="H341" t="n">
         <v>26513</v>
@@ -10345,7 +10345,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G344" t="n">
-        <v>13.7355270385742</v>
+        <v>13.7355251312256</v>
       </c>
       <c r="H344" t="n">
         <v>21920</v>
@@ -10374,7 +10374,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>13.9125289916992</v>
+        <v>13.9125299453735</v>
       </c>
       <c r="H345" t="n">
         <v>32817</v>
@@ -10432,7 +10432,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G347" t="n">
-        <v>13.8488082885742</v>
+        <v>13.8488092422485</v>
       </c>
       <c r="H347" t="n">
         <v>14984</v>
@@ -10461,7 +10461,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G348" t="n">
-        <v>13.7850875854492</v>
+        <v>13.7850847244263</v>
       </c>
       <c r="H348" t="n">
         <v>12738</v>
@@ -10490,7 +10490,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>13.7001256942749</v>
+        <v>13.7001237869263</v>
       </c>
       <c r="H349" t="n">
         <v>41561</v>
@@ -10519,7 +10519,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>13.3815155029297</v>
+        <v>13.3815145492554</v>
       </c>
       <c r="H350" t="n">
         <v>29185</v>
@@ -10548,7 +10548,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>14.0541334152222</v>
+        <v>14.0541315078735</v>
       </c>
       <c r="H351" t="n">
         <v>26703</v>
@@ -10577,7 +10577,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G352" t="n">
-        <v>13.3956785202026</v>
+        <v>13.3956775665283</v>
       </c>
       <c r="H352" t="n">
         <v>20652</v>
@@ -10606,7 +10606,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G353" t="n">
-        <v>13.7072067260742</v>
+        <v>13.7072048187256</v>
       </c>
       <c r="H353" t="n">
         <v>19542</v>
@@ -10635,7 +10635,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G354" t="n">
-        <v>13.6930456161499</v>
+        <v>13.6930446624756</v>
       </c>
       <c r="H354" t="n">
         <v>17696</v>
@@ -10664,7 +10664,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G355" t="n">
-        <v>13.9691705703735</v>
+        <v>13.9691696166992</v>
       </c>
       <c r="H355" t="n">
         <v>22189</v>
@@ -10693,7 +10693,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G356" t="n">
-        <v>14.0470552444458</v>
+        <v>14.0470533370972</v>
       </c>
       <c r="H356" t="n">
         <v>13430</v>
@@ -10722,7 +10722,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>14.0541334152222</v>
+        <v>14.0541315078735</v>
       </c>
       <c r="H357" t="n">
         <v>7547</v>
@@ -10751,7 +10751,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>14.0541334152222</v>
+        <v>14.0541315078735</v>
       </c>
       <c r="H358" t="n">
         <v>5214</v>
@@ -10780,7 +10780,7 @@
         <v>19.8299999237061</v>
       </c>
       <c r="G359" t="n">
-        <v>14.0399732589722</v>
+        <v>14.0399742126465</v>
       </c>
       <c r="H359" t="n">
         <v>8147</v>
@@ -10809,7 +10809,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>13.9125289916992</v>
+        <v>13.9125299453735</v>
       </c>
       <c r="H360" t="n">
         <v>12410</v>
@@ -10838,7 +10838,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G361" t="n">
-        <v>13.9762487411499</v>
+        <v>13.9762516021729</v>
       </c>
       <c r="H361" t="n">
         <v>14178</v>
@@ -10896,7 +10896,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>14.2594566345215</v>
+        <v>14.2594585418701</v>
       </c>
       <c r="H363" t="n">
         <v>21031</v>
@@ -10925,7 +10925,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>15.0099573135376</v>
+        <v>15.009955406189</v>
       </c>
       <c r="H364" t="n">
         <v>23328</v>
@@ -10954,7 +10954,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G365" t="n">
-        <v>15.5126447677612</v>
+        <v>15.5126466751099</v>
       </c>
       <c r="H365" t="n">
         <v>23331</v>
@@ -11012,7 +11012,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G367" t="n">
-        <v>15.0382776260376</v>
+        <v>15.038275718689</v>
       </c>
       <c r="H367" t="n">
         <v>16809</v>
@@ -11041,7 +11041,7 @@
         <v>21</v>
       </c>
       <c r="G368" t="n">
-        <v>14.8683519363403</v>
+        <v>14.8683528900146</v>
       </c>
       <c r="H368" t="n">
         <v>16919</v>
@@ -11070,7 +11070,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G369" t="n">
-        <v>14.6063852310181</v>
+        <v>14.6063842773438</v>
       </c>
       <c r="H369" t="n">
         <v>17526</v>
@@ -11157,7 +11157,7 @@
         <v>21.1700000762939</v>
       </c>
       <c r="G372" t="n">
-        <v>14.9887161254883</v>
+        <v>14.9887142181396</v>
       </c>
       <c r="H372" t="n">
         <v>12413</v>
@@ -11215,7 +11215,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G374" t="n">
-        <v>14.755069732666</v>
+        <v>14.7550706863403</v>
       </c>
       <c r="H374" t="n">
         <v>23760</v>
@@ -11302,7 +11302,7 @@
         <v>21.1100006103516</v>
       </c>
       <c r="G377" t="n">
-        <v>14.946234703064</v>
+        <v>14.9462327957153</v>
       </c>
       <c r="H377" t="n">
         <v>6742</v>
@@ -11331,7 +11331,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G378" t="n">
-        <v>14.854190826416</v>
+        <v>14.8541927337646</v>
       </c>
       <c r="H378" t="n">
         <v>3927</v>
@@ -11360,7 +11360,7 @@
         <v>20.5100002288818</v>
       </c>
       <c r="G379" t="n">
-        <v>14.5214233398438</v>
+        <v>14.5214262008667</v>
       </c>
       <c r="H379" t="n">
         <v>21322</v>
@@ -11447,7 +11447,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>14.7975511550903</v>
+        <v>14.797550201416</v>
       </c>
       <c r="H382" t="n">
         <v>11705</v>
@@ -11476,7 +11476,7 @@
         <v>21</v>
       </c>
       <c r="G383" t="n">
-        <v>14.8683519363403</v>
+        <v>14.8683528900146</v>
       </c>
       <c r="H383" t="n">
         <v>11376</v>
@@ -11563,7 +11563,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G386" t="n">
-        <v>14.7125883102417</v>
+        <v>14.7125902175903</v>
       </c>
       <c r="H386" t="n">
         <v>2901</v>
@@ -11592,7 +11592,7 @@
         <v>21</v>
       </c>
       <c r="G387" t="n">
-        <v>14.8683519363403</v>
+        <v>14.8683528900146</v>
       </c>
       <c r="H387" t="n">
         <v>8598</v>
@@ -11621,7 +11621,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G388" t="n">
-        <v>14.755069732666</v>
+        <v>14.7550706863403</v>
       </c>
       <c r="H388" t="n">
         <v>1900</v>
@@ -11708,7 +11708,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>14.7975511550903</v>
+        <v>14.797550201416</v>
       </c>
       <c r="H391" t="n">
         <v>4081</v>
@@ -11737,7 +11737,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G392" t="n">
-        <v>14.7125883102417</v>
+        <v>14.7125902175903</v>
       </c>
       <c r="H392" t="n">
         <v>4824</v>
@@ -11766,7 +11766,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G393" t="n">
-        <v>15.3356428146362</v>
+        <v>15.3356409072876</v>
       </c>
       <c r="H393" t="n">
         <v>10510</v>
@@ -11795,7 +11795,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>15.3639640808105</v>
+        <v>15.3639631271362</v>
       </c>
       <c r="H394" t="n">
         <v>9327</v>
@@ -11911,7 +11911,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G398" t="n">
-        <v>15.6117677688599</v>
+        <v>15.6117715835571</v>
       </c>
       <c r="H398" t="n">
         <v>12264</v>
@@ -12027,7 +12027,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>14.9391536712646</v>
+        <v>14.9391555786133</v>
       </c>
       <c r="H402" t="n">
         <v>7384</v>
@@ -12056,7 +12056,7 @@
         <v>21.1900005340576</v>
       </c>
       <c r="G403" t="n">
-        <v>15.0028762817383</v>
+        <v>15.002875328064</v>
       </c>
       <c r="H403" t="n">
         <v>5195</v>
@@ -12085,7 +12085,7 @@
         <v>21.0699996948242</v>
       </c>
       <c r="G404" t="n">
-        <v>14.917911529541</v>
+        <v>14.9179134368896</v>
       </c>
       <c r="H404" t="n">
         <v>6186</v>
@@ -12114,7 +12114,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G405" t="n">
-        <v>14.840030670166</v>
+        <v>14.8400316238403</v>
       </c>
       <c r="H405" t="n">
         <v>7724</v>
@@ -12172,7 +12172,7 @@
         <v>21</v>
       </c>
       <c r="G407" t="n">
-        <v>14.8683519363403</v>
+        <v>14.8683528900146</v>
       </c>
       <c r="H407" t="n">
         <v>4124</v>
@@ -12201,7 +12201,7 @@
         <v>21</v>
       </c>
       <c r="G408" t="n">
-        <v>14.8683519363403</v>
+        <v>14.8683528900146</v>
       </c>
       <c r="H408" t="n">
         <v>1716</v>
@@ -12288,7 +12288,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G411" t="n">
-        <v>14.9249954223633</v>
+        <v>14.9249925613403</v>
       </c>
       <c r="H411" t="n">
         <v>2495</v>
@@ -12317,7 +12317,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>14.5851449966431</v>
+        <v>14.5851469039917</v>
       </c>
       <c r="H412" t="n">
         <v>8975</v>
@@ -12462,7 +12462,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G417" t="n">
-        <v>14.6488676071167</v>
+        <v>14.6488666534424</v>
       </c>
       <c r="H417" t="n">
         <v>1133</v>
@@ -12520,7 +12520,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>14.6559476852417</v>
+        <v>14.6559448242188</v>
       </c>
       <c r="H419" t="n">
         <v>1679</v>
@@ -12549,7 +12549,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>14.5851449966431</v>
+        <v>14.5851469039917</v>
       </c>
       <c r="H420" t="n">
         <v>5446</v>
@@ -12578,7 +12578,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>14.3727388381958</v>
+        <v>14.3727378845215</v>
       </c>
       <c r="H421" t="n">
         <v>9020</v>
@@ -12607,7 +12607,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>14.4435443878174</v>
+        <v>14.4435434341431</v>
       </c>
       <c r="H422" t="n">
         <v>2219</v>
@@ -12636,7 +12636,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G423" t="n">
-        <v>14.3868999481201</v>
+        <v>14.3869009017944</v>
       </c>
       <c r="H423" t="n">
         <v>2918</v>
@@ -12665,7 +12665,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G424" t="n">
-        <v>14.578067779541</v>
+        <v>14.5780649185181</v>
       </c>
       <c r="H424" t="n">
         <v>1164</v>
@@ -12694,7 +12694,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G425" t="n">
-        <v>14.1886577606201</v>
+        <v>14.1886558532715</v>
       </c>
       <c r="H425" t="n">
         <v>9381</v>
@@ -12723,7 +12723,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G426" t="n">
-        <v>14.5426645278931</v>
+        <v>14.5426635742188</v>
       </c>
       <c r="H426" t="n">
         <v>8692</v>
@@ -12781,7 +12781,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>14.3019399642944</v>
+        <v>14.3019390106201</v>
       </c>
       <c r="H428" t="n">
         <v>7453</v>
@@ -12810,7 +12810,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G429" t="n">
-        <v>13.9762487411499</v>
+        <v>13.9762516021729</v>
       </c>
       <c r="H429" t="n">
         <v>11201</v>
@@ -12868,7 +12868,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G431" t="n">
-        <v>14.3019399642944</v>
+        <v>14.3019390106201</v>
       </c>
       <c r="H431" t="n">
         <v>5938</v>
@@ -12897,7 +12897,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>14.5355854034424</v>
+        <v>14.535587310791</v>
       </c>
       <c r="H432" t="n">
         <v>11289</v>
@@ -12926,7 +12926,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G433" t="n">
-        <v>14.5355854034424</v>
+        <v>14.535587310791</v>
       </c>
       <c r="H433" t="n">
         <v>6217</v>
@@ -12984,7 +12984,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>14.6559476852417</v>
+        <v>14.6559448242188</v>
       </c>
       <c r="H435" t="n">
         <v>17621</v>
@@ -13042,7 +13042,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G437" t="n">
-        <v>15.0382776260376</v>
+        <v>15.038275718689</v>
       </c>
       <c r="H437" t="n">
         <v>15846</v>
@@ -13100,7 +13100,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1090803146362</v>
+        <v>15.1090774536133</v>
       </c>
       <c r="H439" t="n">
         <v>21722</v>
@@ -13129,7 +13129,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G440" t="n">
-        <v>15.5126447677612</v>
+        <v>15.5126466751099</v>
       </c>
       <c r="H440" t="n">
         <v>11636</v>
@@ -13158,7 +13158,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G441" t="n">
-        <v>15.9232969284058</v>
+        <v>15.9232978820801</v>
       </c>
       <c r="H441" t="n">
         <v>31239</v>
@@ -13274,7 +13274,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G445" t="n">
-        <v>18.0119495391846</v>
+        <v>18.0119476318359</v>
       </c>
       <c r="H445" t="n">
         <v>32651</v>
@@ -13332,7 +13332,7 @@
         <v>25.1900005340576</v>
       </c>
       <c r="G447" t="n">
-        <v>17.8349437713623</v>
+        <v>17.8349418640137</v>
       </c>
       <c r="H447" t="n">
         <v>17315</v>
@@ -13390,7 +13390,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G449" t="n">
-        <v>17.8066215515137</v>
+        <v>17.8066234588623</v>
       </c>
       <c r="H449" t="n">
         <v>15515</v>
@@ -13419,7 +13419,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>17.5942192077637</v>
+        <v>17.594217300415</v>
       </c>
       <c r="H450" t="n">
         <v>19676</v>
@@ -13477,7 +13477,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G452" t="n">
-        <v>17.6296157836914</v>
+        <v>17.6296195983887</v>
       </c>
       <c r="H452" t="n">
         <v>8164</v>
@@ -13593,7 +13593,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G456" t="n">
-        <v>17.3888931274414</v>
+        <v>17.3888912200928</v>
       </c>
       <c r="H456" t="n">
         <v>7934</v>
@@ -13680,7 +13680,7 @@
         <v>24.25</v>
       </c>
       <c r="G459" t="n">
-        <v>17.1694107055664</v>
+        <v>17.1694087982178</v>
       </c>
       <c r="H459" t="n">
         <v>23508</v>
@@ -13796,7 +13796,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G463" t="n">
-        <v>16.9216041564941</v>
+        <v>16.9216022491455</v>
       </c>
       <c r="H463" t="n">
         <v>6420</v>
@@ -13825,7 +13825,7 @@
         <v>23.5699996948242</v>
       </c>
       <c r="G464" t="n">
-        <v>16.6879577636719</v>
+        <v>16.6879558563232</v>
       </c>
       <c r="H464" t="n">
         <v>18210</v>
@@ -13854,7 +13854,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G465" t="n">
-        <v>16.9003620147705</v>
+        <v>16.9003601074219</v>
       </c>
       <c r="H465" t="n">
         <v>8780</v>
@@ -13883,7 +13883,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G466" t="n">
-        <v>16.7375144958496</v>
+        <v>16.7375164031982</v>
       </c>
       <c r="H466" t="n">
         <v>10368</v>
@@ -13912,7 +13912,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G467" t="n">
-        <v>16.9640789031982</v>
+        <v>16.9640827178955</v>
       </c>
       <c r="H467" t="n">
         <v>27238</v>
@@ -14028,7 +14028,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G471" t="n">
-        <v>17.0348815917969</v>
+        <v>17.0348834991455</v>
       </c>
       <c r="H471" t="n">
         <v>11850</v>
@@ -14057,7 +14057,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G472" t="n">
-        <v>17.0136432647705</v>
+        <v>17.0136451721191</v>
       </c>
       <c r="H472" t="n">
         <v>6691</v>
@@ -14144,7 +14144,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>16.9216041564941</v>
+        <v>16.9216022491455</v>
       </c>
       <c r="H475" t="n">
         <v>13981</v>
@@ -14173,7 +14173,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>16.8083171844482</v>
+        <v>16.8083152770996</v>
       </c>
       <c r="H476" t="n">
         <v>13569</v>
@@ -14202,7 +14202,7 @@
         <v>22.9400005340576</v>
       </c>
       <c r="G477" t="n">
-        <v>16.2419052124023</v>
+        <v>16.2419033050537</v>
       </c>
       <c r="H477" t="n">
         <v>30389</v>
@@ -14231,7 +14231,7 @@
         <v>22.9899997711182</v>
       </c>
       <c r="G478" t="n">
-        <v>16.2773056030273</v>
+        <v>16.277307510376</v>
       </c>
       <c r="H478" t="n">
         <v>7291</v>
@@ -14260,7 +14260,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>16.567590713501</v>
+        <v>16.5675926208496</v>
       </c>
       <c r="H479" t="n">
         <v>15551</v>
@@ -14318,7 +14318,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G481" t="n">
-        <v>15.3781213760376</v>
+        <v>15.3781232833862</v>
       </c>
       <c r="H481" t="n">
         <v>25164</v>
@@ -14347,7 +14347,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G482" t="n">
-        <v>15.7746124267578</v>
+        <v>15.7746143341064</v>
       </c>
       <c r="H482" t="n">
         <v>15379</v>
@@ -14463,7 +14463,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G486" t="n">
-        <v>15.9232969284058</v>
+        <v>15.9232978820801</v>
       </c>
       <c r="H486" t="n">
         <v>24126</v>
@@ -14521,7 +14521,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G488" t="n">
-        <v>15.9232969284058</v>
+        <v>15.9232978820801</v>
       </c>
       <c r="H488" t="n">
         <v>13194</v>
@@ -14550,7 +14550,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G489" t="n">
-        <v>15.9587020874023</v>
+        <v>15.9587001800537</v>
       </c>
       <c r="H489" t="n">
         <v>12045</v>
@@ -14608,7 +14608,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G491" t="n">
-        <v>16.1640243530273</v>
+        <v>16.1640224456787</v>
       </c>
       <c r="H491" t="n">
         <v>10640</v>
@@ -14666,7 +14666,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G493" t="n">
-        <v>15.7321319580078</v>
+        <v>15.7321338653564</v>
       </c>
       <c r="H493" t="n">
         <v>9837</v>
@@ -14724,7 +14724,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G495" t="n">
-        <v>16.0648994445801</v>
+        <v>16.0648975372314</v>
       </c>
       <c r="H495" t="n">
         <v>10878</v>
@@ -14782,7 +14782,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G497" t="n">
-        <v>15.5409679412842</v>
+        <v>15.5409698486328</v>
       </c>
       <c r="H497" t="n">
         <v>9415</v>
@@ -14840,7 +14840,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G499" t="n">
-        <v>16.1003017425537</v>
+        <v>16.1002998352051</v>
       </c>
       <c r="H499" t="n">
         <v>10783</v>
@@ -14869,7 +14869,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G500" t="n">
-        <v>15.8595752716064</v>
+        <v>15.8595771789551</v>
       </c>
       <c r="H500" t="n">
         <v>8238</v>
@@ -14898,7 +14898,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>15.8595752716064</v>
+        <v>15.8595771789551</v>
       </c>
       <c r="H501" t="n">
         <v>6008</v>
@@ -14985,7 +14985,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G504" t="n">
-        <v>15.5197267532349</v>
+        <v>15.5197248458862</v>
       </c>
       <c r="H504" t="n">
         <v>4813</v>
@@ -15014,7 +15014,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G505" t="n">
-        <v>15.3002424240112</v>
+        <v>15.3002443313599</v>
       </c>
       <c r="H505" t="n">
         <v>6673</v>
@@ -15072,7 +15072,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G507" t="n">
-        <v>15.1444787979126</v>
+        <v>15.144476890564</v>
       </c>
       <c r="H507" t="n">
         <v>4411</v>
@@ -15130,7 +15130,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G509" t="n">
-        <v>14.9249954223633</v>
+        <v>14.9249925613403</v>
       </c>
       <c r="H509" t="n">
         <v>17619</v>
@@ -15188,7 +15188,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>15.2931652069092</v>
+        <v>15.2931632995605</v>
       </c>
       <c r="H511" t="n">
         <v>11388</v>
@@ -15217,7 +15217,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G512" t="n">
-        <v>15.6613302230835</v>
+        <v>15.6613340377808</v>
       </c>
       <c r="H512" t="n">
         <v>6481</v>
@@ -15246,7 +15246,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>15.8949747085571</v>
+        <v>15.8949785232544</v>
       </c>
       <c r="H513" t="n">
         <v>5579</v>
@@ -15275,7 +15275,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G514" t="n">
-        <v>15.8241729736328</v>
+        <v>15.8241748809814</v>
       </c>
       <c r="H514" t="n">
         <v>5892</v>
@@ -15362,7 +15362,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G517" t="n">
-        <v>16.4259910583496</v>
+        <v>16.425989151001</v>
       </c>
       <c r="H517" t="n">
         <v>8904</v>
@@ -15478,7 +15478,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>16.3905849456787</v>
+        <v>16.390588760376</v>
       </c>
       <c r="H521" t="n">
         <v>5601</v>
@@ -15623,7 +15623,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>16.3551902770996</v>
+        <v>16.355188369751</v>
       </c>
       <c r="H526" t="n">
         <v>4876</v>
@@ -15652,7 +15652,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>16.496789932251</v>
+        <v>16.4967918395996</v>
       </c>
       <c r="H527" t="n">
         <v>9410</v>
@@ -15681,7 +15681,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G528" t="n">
-        <v>16.496789932251</v>
+        <v>16.4967918395996</v>
       </c>
       <c r="H528" t="n">
         <v>7588</v>
@@ -15739,7 +15739,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>16.8507976531982</v>
+        <v>16.8507995605469</v>
       </c>
       <c r="H530" t="n">
         <v>21127</v>
@@ -15768,7 +15768,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>17.0632038116455</v>
+        <v>17.0632057189941</v>
       </c>
       <c r="H531" t="n">
         <v>18691</v>
@@ -15797,7 +15797,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>16.496789932251</v>
+        <v>16.4967918395996</v>
       </c>
       <c r="H532" t="n">
         <v>10158</v>
@@ -15826,7 +15826,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>16.6029968261719</v>
+        <v>16.6029949188232</v>
       </c>
       <c r="H533" t="n">
         <v>4053</v>
@@ -15855,7 +15855,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>16.3905849456787</v>
+        <v>16.390588760376</v>
       </c>
       <c r="H534" t="n">
         <v>10434</v>
@@ -15884,7 +15884,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G535" t="n">
-        <v>16.496789932251</v>
+        <v>16.4967918395996</v>
       </c>
       <c r="H535" t="n">
         <v>6175</v>
@@ -15971,7 +15971,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G538" t="n">
-        <v>15.8595752716064</v>
+        <v>15.8595771789551</v>
       </c>
       <c r="H538" t="n">
         <v>6921</v>
@@ -16029,7 +16029,7 @@
         <v>22</v>
       </c>
       <c r="G540" t="n">
-        <v>15.5763702392578</v>
+        <v>15.5763683319092</v>
       </c>
       <c r="H540" t="n">
         <v>8115</v>
@@ -16058,7 +16058,7 @@
         <v>22</v>
       </c>
       <c r="G541" t="n">
-        <v>15.5763702392578</v>
+        <v>15.5763683319092</v>
       </c>
       <c r="H541" t="n">
         <v>4539</v>
@@ -16116,7 +16116,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>15.2931652069092</v>
+        <v>15.2931632995605</v>
       </c>
       <c r="H543" t="n">
         <v>4408</v>
@@ -16145,7 +16145,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>15.2931652069092</v>
+        <v>15.2931632995605</v>
       </c>
       <c r="H544" t="n">
         <v>5884</v>
@@ -16174,7 +16174,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>15.3639640808105</v>
+        <v>15.3639631271362</v>
       </c>
       <c r="H545" t="n">
         <v>949</v>
@@ -16232,7 +16232,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>15.2931652069092</v>
+        <v>15.2931632995605</v>
       </c>
       <c r="H547" t="n">
         <v>2724</v>
@@ -16348,7 +16348,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>15.0099573135376</v>
+        <v>15.009955406189</v>
       </c>
       <c r="H551" t="n">
         <v>5834</v>
@@ -16377,7 +16377,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>14.9391536712646</v>
+        <v>14.9391555786133</v>
       </c>
       <c r="H552" t="n">
         <v>12149</v>
@@ -16522,7 +16522,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G557" t="n">
-        <v>15.5409679412842</v>
+        <v>15.5409698486328</v>
       </c>
       <c r="H557" t="n">
         <v>10920</v>
@@ -16667,7 +16667,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>16.6029968261719</v>
+        <v>16.6029949188232</v>
       </c>
       <c r="H562" t="n">
         <v>15911</v>
@@ -16696,7 +16696,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>16.8507976531982</v>
+        <v>16.8507995605469</v>
       </c>
       <c r="H563" t="n">
         <v>9961</v>
@@ -16783,7 +16783,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>16.6029968261719</v>
+        <v>16.6029949188232</v>
       </c>
       <c r="H566" t="n">
         <v>6822</v>
@@ -16812,7 +16812,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>16.7445964813232</v>
+        <v>16.7445945739746</v>
       </c>
       <c r="H567" t="n">
         <v>1395</v>
@@ -16957,7 +16957,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G572" t="n">
-        <v>16.7091960906982</v>
+        <v>16.7091941833496</v>
       </c>
       <c r="H572" t="n">
         <v>3927</v>
@@ -16986,7 +16986,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G573" t="n">
-        <v>16.567590713501</v>
+        <v>16.5675926208496</v>
       </c>
       <c r="H573" t="n">
         <v>1687</v>
@@ -17015,7 +17015,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G574" t="n">
-        <v>16.496789932251</v>
+        <v>16.4967918395996</v>
       </c>
       <c r="H574" t="n">
         <v>3962</v>
@@ -17044,7 +17044,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>16.496789932251</v>
+        <v>16.4967918395996</v>
       </c>
       <c r="H575" t="n">
         <v>912</v>
@@ -17073,7 +17073,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>16.7091960906982</v>
+        <v>16.7091941833496</v>
       </c>
       <c r="H576" t="n">
         <v>965</v>
@@ -17102,7 +17102,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>16.6029968261719</v>
+        <v>16.6029949188232</v>
       </c>
       <c r="H577" t="n">
         <v>2804</v>
@@ -17160,7 +17160,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>16.567590713501</v>
+        <v>16.5675926208496</v>
       </c>
       <c r="H579" t="n">
         <v>9918</v>
@@ -17218,7 +17218,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G581" t="n">
-        <v>16.4259910583496</v>
+        <v>16.425989151001</v>
       </c>
       <c r="H581" t="n">
         <v>3770</v>
@@ -17247,7 +17247,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>16.3905849456787</v>
+        <v>16.390588760376</v>
       </c>
       <c r="H582" t="n">
         <v>4111</v>
@@ -17363,7 +17363,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G586" t="n">
-        <v>17.3110103607178</v>
+        <v>17.3110122680664</v>
       </c>
       <c r="H586" t="n">
         <v>12073</v>
@@ -17450,7 +17450,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>16.8862018585205</v>
+        <v>16.8861999511719</v>
       </c>
       <c r="H589" t="n">
         <v>9907</v>
@@ -17508,7 +17508,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G591" t="n">
-        <v>17.3818092346191</v>
+        <v>17.3818111419678</v>
       </c>
       <c r="H591" t="n">
         <v>3273</v>
@@ -17682,7 +17682,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>18.6208381652832</v>
+        <v>18.6208400726318</v>
       </c>
       <c r="H597" t="n">
         <v>20876</v>
@@ -17711,7 +17711,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>19.1320037841797</v>
+        <v>19.1320018768311</v>
       </c>
       <c r="H598" t="n">
         <v>13991</v>
@@ -17740,7 +17740,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G599" t="n">
-        <v>18.8399085998535</v>
+        <v>18.8399105072021</v>
       </c>
       <c r="H599" t="n">
         <v>9619</v>
@@ -17769,7 +17769,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>19.1320037841797</v>
+        <v>19.1320018768311</v>
       </c>
       <c r="H600" t="n">
         <v>9269</v>
@@ -17798,7 +17798,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G601" t="n">
-        <v>19.1320037841797</v>
+        <v>19.1320018768311</v>
       </c>
       <c r="H601" t="n">
         <v>5995</v>
@@ -17885,7 +17885,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G604" t="n">
-        <v>19.2415351867676</v>
+        <v>19.2415370941162</v>
       </c>
       <c r="H604" t="n">
         <v>14195</v>
@@ -18030,7 +18030,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G609" t="n">
-        <v>18.4747943878174</v>
+        <v>18.4747924804688</v>
       </c>
       <c r="H609" t="n">
         <v>29101</v>
@@ -18059,7 +18059,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>18.4747943878174</v>
+        <v>18.4747924804688</v>
       </c>
       <c r="H610" t="n">
         <v>6388</v>
@@ -18146,7 +18146,7 @@
         <v>24</v>
       </c>
       <c r="G613" t="n">
-        <v>17.5254993438721</v>
+        <v>17.5254974365234</v>
       </c>
       <c r="H613" t="n">
         <v>11020</v>
@@ -18233,7 +18233,7 @@
         <v>24</v>
       </c>
       <c r="G616" t="n">
-        <v>17.5254993438721</v>
+        <v>17.5254974365234</v>
       </c>
       <c r="H616" t="n">
         <v>7135</v>
@@ -18262,7 +18262,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>18.4747943878174</v>
+        <v>18.4747924804688</v>
       </c>
       <c r="H617" t="n">
         <v>9371</v>
@@ -18465,7 +18465,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>19.0954914093018</v>
+        <v>19.0954895019531</v>
       </c>
       <c r="H624" t="n">
         <v>6763</v>
@@ -18494,7 +18494,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>19.3875827789307</v>
+        <v>19.387580871582</v>
       </c>
       <c r="H625" t="n">
         <v>8823</v>
@@ -18581,7 +18581,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>19.0954914093018</v>
+        <v>19.0954895019531</v>
       </c>
       <c r="H628" t="n">
         <v>5021</v>
@@ -18610,7 +18610,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>18.9129295349121</v>
+        <v>18.9129314422607</v>
       </c>
       <c r="H629" t="n">
         <v>4095</v>
@@ -18668,7 +18668,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>18.0366592407227</v>
+        <v>18.036657333374</v>
       </c>
       <c r="H631" t="n">
         <v>3517</v>
@@ -18784,7 +18784,7 @@
         <v>25.5</v>
       </c>
       <c r="G635" t="n">
-        <v>18.6208400726318</v>
+        <v>18.6208419799805</v>
       </c>
       <c r="H635" t="n">
         <v>12854</v>
@@ -18813,7 +18813,7 @@
         <v>25.5</v>
       </c>
       <c r="G636" t="n">
-        <v>18.6208400726318</v>
+        <v>18.6208419799805</v>
       </c>
       <c r="H636" t="n">
         <v>3028</v>
@@ -18842,7 +18842,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>19.3145561218262</v>
+        <v>19.3145580291748</v>
       </c>
       <c r="H637" t="n">
         <v>5634</v>
@@ -18871,7 +18871,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>18.3287487030029</v>
+        <v>18.3287506103516</v>
       </c>
       <c r="H638" t="n">
         <v>8277</v>
@@ -18929,7 +18929,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>18.3287487030029</v>
+        <v>18.3287506103516</v>
       </c>
       <c r="H640" t="n">
         <v>1414</v>
@@ -18958,7 +18958,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>18.4747943878174</v>
+        <v>18.4747924804688</v>
       </c>
       <c r="H641" t="n">
         <v>1155</v>
@@ -19016,7 +19016,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>18.3287487030029</v>
+        <v>18.3287506103516</v>
       </c>
       <c r="H643" t="n">
         <v>3316</v>
@@ -19074,7 +19074,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>18.1827068328857</v>
+        <v>18.1827049255371</v>
       </c>
       <c r="H645" t="n">
         <v>3618</v>
@@ -19132,7 +19132,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>18.1461925506592</v>
+        <v>18.1461906433105</v>
       </c>
       <c r="H647" t="n">
         <v>1741</v>
@@ -19190,7 +19190,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>17.7445659637451</v>
+        <v>17.7445678710938</v>
       </c>
       <c r="H649" t="n">
         <v>4017</v>
@@ -19335,7 +19335,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G654" t="n">
-        <v>18.4747943878174</v>
+        <v>18.4747924804688</v>
       </c>
       <c r="H654" t="n">
         <v>10845</v>
@@ -19364,7 +19364,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G655" t="n">
-        <v>18.3652610778809</v>
+        <v>18.3652629852295</v>
       </c>
       <c r="H655" t="n">
         <v>3279</v>
@@ -19393,7 +19393,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>18.2192153930664</v>
+        <v>18.219217300415</v>
       </c>
       <c r="H656" t="n">
         <v>4391</v>
@@ -19480,7 +19480,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G659" t="n">
-        <v>18.3287487030029</v>
+        <v>18.3287506103516</v>
       </c>
       <c r="H659" t="n">
         <v>2461</v>
@@ -19538,7 +19538,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>18.1827068328857</v>
+        <v>18.1827049255371</v>
       </c>
       <c r="H661" t="n">
         <v>14669</v>
@@ -19625,7 +19625,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>18.1461925506592</v>
+        <v>18.1461906433105</v>
       </c>
       <c r="H664" t="n">
         <v>1932</v>
@@ -19654,7 +19654,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>18.2922382354736</v>
+        <v>18.2922401428223</v>
       </c>
       <c r="H665" t="n">
         <v>2449</v>
@@ -19683,7 +19683,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>18.2922382354736</v>
+        <v>18.2922401428223</v>
       </c>
       <c r="H666" t="n">
         <v>2868</v>
@@ -19741,7 +19741,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>18.3652610778809</v>
+        <v>18.3652629852295</v>
       </c>
       <c r="H668" t="n">
         <v>4443</v>
@@ -19770,7 +19770,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>18.3287487030029</v>
+        <v>18.3287506103516</v>
       </c>
       <c r="H669" t="n">
         <v>2283</v>
@@ -19799,7 +19799,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>18.0366592407227</v>
+        <v>18.036657333374</v>
       </c>
       <c r="H670" t="n">
         <v>2848</v>
@@ -19828,7 +19828,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>17.9271221160889</v>
+        <v>17.9271240234375</v>
       </c>
       <c r="H671" t="n">
         <v>1911</v>
@@ -19857,7 +19857,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>17.9271221160889</v>
+        <v>17.9271240234375</v>
       </c>
       <c r="H672" t="n">
         <v>1106</v>
@@ -19915,7 +19915,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G674" t="n">
-        <v>18.4747943878174</v>
+        <v>18.4747924804688</v>
       </c>
       <c r="H674" t="n">
         <v>4055</v>
@@ -20147,7 +20147,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>18.2922382354736</v>
+        <v>18.2922401428223</v>
       </c>
       <c r="H682" t="n">
         <v>3696</v>
@@ -20176,7 +20176,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G683" t="n">
-        <v>18.2922382354736</v>
+        <v>18.2922401428223</v>
       </c>
       <c r="H683" t="n">
         <v>2115</v>
@@ -20205,7 +20205,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G684" t="n">
-        <v>18.2192153930664</v>
+        <v>18.219217300415</v>
       </c>
       <c r="H684" t="n">
         <v>6885</v>
@@ -20234,7 +20234,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G685" t="n">
-        <v>18.1827068328857</v>
+        <v>18.1827049255371</v>
       </c>
       <c r="H685" t="n">
         <v>4547</v>
@@ -20292,7 +20292,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>18.8399085998535</v>
+        <v>18.8399105072021</v>
       </c>
       <c r="H687" t="n">
         <v>6209</v>
@@ -20321,7 +20321,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>18.8399085998535</v>
+        <v>18.8399105072021</v>
       </c>
       <c r="H688" t="n">
         <v>31155</v>
@@ -20350,7 +20350,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G689" t="n">
-        <v>18.0366592407227</v>
+        <v>18.036657333374</v>
       </c>
       <c r="H689" t="n">
         <v>4579</v>
@@ -20437,7 +20437,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>18.1827068328857</v>
+        <v>18.1827049255371</v>
       </c>
       <c r="H692" t="n">
         <v>4532</v>
@@ -20495,7 +20495,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>18.2192153930664</v>
+        <v>18.219217300415</v>
       </c>
       <c r="H694" t="n">
         <v>2014</v>
@@ -20524,7 +20524,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>18.0366592407227</v>
+        <v>18.036657333374</v>
       </c>
       <c r="H695" t="n">
         <v>4168</v>
@@ -20640,7 +20640,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>18.1827068328857</v>
+        <v>18.1827049255371</v>
       </c>
       <c r="H699" t="n">
         <v>1264</v>
@@ -20698,7 +20698,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>17.63503074646</v>
+        <v>17.6350326538086</v>
       </c>
       <c r="H701" t="n">
         <v>6754</v>
@@ -20727,7 +20727,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>17.63503074646</v>
+        <v>17.6350326538086</v>
       </c>
       <c r="H702" t="n">
         <v>4229</v>
@@ -20756,7 +20756,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G703" t="n">
-        <v>17.7445659637451</v>
+        <v>17.7445678710938</v>
       </c>
       <c r="H703" t="n">
         <v>2829</v>
@@ -20785,7 +20785,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>18.0001487731934</v>
+        <v>18.0001468658447</v>
       </c>
       <c r="H704" t="n">
         <v>1558</v>
@@ -20814,7 +20814,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G705" t="n">
-        <v>17.63503074646</v>
+        <v>17.6350326538086</v>
       </c>
       <c r="H705" t="n">
         <v>1635</v>
@@ -20959,7 +20959,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>14.8236503601074</v>
+        <v>14.8236494064331</v>
       </c>
       <c r="H710" t="n">
         <v>7148</v>
@@ -20988,7 +20988,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>14.6410913467407</v>
+        <v>14.641092300415</v>
       </c>
       <c r="H711" t="n">
         <v>8704</v>
@@ -21017,7 +21017,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>14.8236503601074</v>
+        <v>14.8236494064331</v>
       </c>
       <c r="H712" t="n">
         <v>12194</v>
@@ -21104,7 +21104,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="n">
-        <v>15.3348121643066</v>
+        <v>15.334810256958</v>
       </c>
       <c r="H715" t="n">
         <v>4866</v>
@@ -21133,7 +21133,7 @@
         <v>20.25</v>
       </c>
       <c r="G716" t="n">
-        <v>14.7871408462524</v>
+        <v>14.7871379852295</v>
       </c>
       <c r="H716" t="n">
         <v>12724</v>
@@ -21162,7 +21162,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>14.677604675293</v>
+        <v>14.6776056289673</v>
       </c>
       <c r="H717" t="n">
         <v>4356</v>
@@ -21191,7 +21191,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>14.7141141891479</v>
+        <v>14.7141170501709</v>
       </c>
       <c r="H718" t="n">
         <v>11313</v>
@@ -21220,7 +21220,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>14.458535194397</v>
+        <v>14.4585361480713</v>
       </c>
       <c r="H719" t="n">
         <v>7139</v>
@@ -21249,7 +21249,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G720" t="n">
-        <v>14.458535194397</v>
+        <v>14.4585361480713</v>
       </c>
       <c r="H720" t="n">
         <v>8003</v>
@@ -21365,7 +21365,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>14.677604675293</v>
+        <v>14.6776056289673</v>
       </c>
       <c r="H724" t="n">
         <v>4155</v>
@@ -21423,7 +21423,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G726" t="n">
-        <v>14.9331846237183</v>
+        <v>14.9331865310669</v>
       </c>
       <c r="H726" t="n">
         <v>5117</v>
@@ -21452,7 +21452,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>15.9189920425415</v>
+        <v>15.9189939498901</v>
       </c>
       <c r="H727" t="n">
         <v>7386</v>
@@ -21481,7 +21481,7 @@
         <v>21</v>
       </c>
       <c r="G728" t="n">
-        <v>15.3348121643066</v>
+        <v>15.334810256958</v>
       </c>
       <c r="H728" t="n">
         <v>6646</v>
@@ -21539,7 +21539,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>15.5903930664062</v>
+        <v>15.5903911590576</v>
       </c>
       <c r="H730" t="n">
         <v>2078</v>
@@ -21568,7 +21568,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>15.4443454742432</v>
+        <v>15.4443445205688</v>
       </c>
       <c r="H731" t="n">
         <v>1961</v>
@@ -21597,7 +21597,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>15.3713216781616</v>
+        <v>15.3713235855103</v>
       </c>
       <c r="H732" t="n">
         <v>2126</v>
@@ -21626,7 +21626,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>15.2252750396729</v>
+        <v>15.2252769470215</v>
       </c>
       <c r="H733" t="n">
         <v>8821</v>
@@ -21771,7 +21771,7 @@
         <v>20.5</v>
       </c>
       <c r="G738" t="n">
-        <v>14.9696950912476</v>
+        <v>14.9696960449219</v>
       </c>
       <c r="H738" t="n">
         <v>5159</v>
@@ -21800,7 +21800,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G739" t="n">
-        <v>14.8966732025146</v>
+        <v>14.896674156189</v>
       </c>
       <c r="H739" t="n">
         <v>1616</v>
@@ -21829,7 +21829,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>14.8236503601074</v>
+        <v>14.8236494064331</v>
       </c>
       <c r="H740" t="n">
         <v>8004</v>
@@ -21858,7 +21858,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>14.860161781311</v>
+        <v>14.8601608276367</v>
       </c>
       <c r="H741" t="n">
         <v>371</v>
@@ -21887,7 +21887,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G742" t="n">
-        <v>15.3713216781616</v>
+        <v>15.3713235855103</v>
       </c>
       <c r="H742" t="n">
         <v>4528</v>
@@ -21916,7 +21916,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>15.5903930664062</v>
+        <v>15.5903911590576</v>
       </c>
       <c r="H743" t="n">
         <v>6640</v>
@@ -21945,7 +21945,7 @@
         <v>21.25</v>
       </c>
       <c r="G744" t="n">
-        <v>15.5173654556274</v>
+        <v>15.5173683166504</v>
       </c>
       <c r="H744" t="n">
         <v>2216</v>
@@ -22003,7 +22003,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>15.5903930664062</v>
+        <v>15.5903911590576</v>
       </c>
       <c r="H746" t="n">
         <v>7269</v>
@@ -22061,7 +22061,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G748" t="n">
-        <v>15.553879737854</v>
+        <v>15.5538778305054</v>
       </c>
       <c r="H748" t="n">
         <v>4179</v>
@@ -22090,7 +22090,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>15.4443454742432</v>
+        <v>15.4443445205688</v>
       </c>
       <c r="H749" t="n">
         <v>1016</v>
@@ -22148,7 +22148,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>15.5903930664062</v>
+        <v>15.5903911590576</v>
       </c>
       <c r="H751" t="n">
         <v>1</v>
@@ -22206,7 +22206,7 @@
         <v>21</v>
       </c>
       <c r="G753" t="n">
-        <v>15.3348121643066</v>
+        <v>15.334810256958</v>
       </c>
       <c r="H753" t="n">
         <v>3386</v>
@@ -22264,7 +22264,7 @@
         <v>21</v>
       </c>
       <c r="G755" t="n">
-        <v>15.3348121643066</v>
+        <v>15.334810256958</v>
       </c>
       <c r="H755" t="n">
         <v>690</v>
@@ -22293,7 +22293,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>15.2252750396729</v>
+        <v>15.2252769470215</v>
       </c>
       <c r="H756" t="n">
         <v>5044</v>
@@ -22467,7 +22467,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G762" t="n">
-        <v>14.4001159667969</v>
+        <v>14.4001178741455</v>
       </c>
       <c r="H762" t="n">
         <v>2544</v>
@@ -22496,7 +22496,7 @@
         <v>20.25</v>
       </c>
       <c r="G763" t="n">
-        <v>14.7871408462524</v>
+        <v>14.7871379852295</v>
       </c>
       <c r="H763" t="n">
         <v>3694</v>
@@ -22525,7 +22525,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>14.8966732025146</v>
+        <v>14.896674156189</v>
       </c>
       <c r="H764" t="n">
         <v>1448</v>
@@ -22554,7 +22554,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G765" t="n">
-        <v>15.115743637085</v>
+        <v>15.1157417297363</v>
       </c>
       <c r="H765" t="n">
         <v>350</v>
@@ -22583,7 +22583,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>15.4443454742432</v>
+        <v>15.4443445205688</v>
       </c>
       <c r="H766" t="n">
         <v>1563</v>
@@ -22612,7 +22612,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>15.4443454742432</v>
+        <v>15.4443445205688</v>
       </c>
       <c r="H767" t="n">
         <v>976</v>
@@ -22670,7 +22670,7 @@
         <v>21</v>
       </c>
       <c r="G769" t="n">
-        <v>15.3348121643066</v>
+        <v>15.334810256958</v>
       </c>
       <c r="H769" t="n">
         <v>435</v>
@@ -22699,7 +22699,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G770" t="n">
-        <v>15.7729501724243</v>
+        <v>15.7729482650757</v>
       </c>
       <c r="H770" t="n">
         <v>10593</v>
@@ -22757,7 +22757,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>16.2110862731934</v>
+        <v>16.2110843658447</v>
       </c>
       <c r="H772" t="n">
         <v>12994</v>
@@ -22786,7 +22786,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>16.028528213501</v>
+        <v>16.0285301208496</v>
       </c>
       <c r="H773" t="n">
         <v>16957</v>
@@ -22815,7 +22815,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>16.2110862731934</v>
+        <v>16.2110843658447</v>
       </c>
       <c r="H774" t="n">
         <v>4710</v>
@@ -22844,7 +22844,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>16.1380634307861</v>
+        <v>16.1380615234375</v>
       </c>
       <c r="H775" t="n">
         <v>15794</v>
@@ -22873,7 +22873,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>16.028528213501</v>
+        <v>16.0285301208496</v>
       </c>
       <c r="H776" t="n">
         <v>3039</v>
@@ -22989,7 +22989,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>16.1380634307861</v>
+        <v>16.1380615234375</v>
       </c>
       <c r="H780" t="n">
         <v>84009</v>
@@ -23076,7 +23076,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>15.2252750396729</v>
+        <v>15.2252769470215</v>
       </c>
       <c r="H783" t="n">
         <v>9187</v>
@@ -23105,7 +23105,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G784" t="n">
-        <v>15.4078350067139</v>
+        <v>15.4078359603882</v>
       </c>
       <c r="H784" t="n">
         <v>4143</v>
@@ -23134,7 +23134,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>15.2252750396729</v>
+        <v>15.2252769470215</v>
       </c>
       <c r="H785" t="n">
         <v>6779</v>
@@ -23163,7 +23163,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G786" t="n">
-        <v>15.115743637085</v>
+        <v>15.1157417297363</v>
       </c>
       <c r="H786" t="n">
         <v>3460</v>
@@ -23192,7 +23192,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G787" t="n">
-        <v>15.0427188873291</v>
+        <v>15.0427207946777</v>
       </c>
       <c r="H787" t="n">
         <v>5312</v>
@@ -23221,7 +23221,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>14.8966732025146</v>
+        <v>14.896674156189</v>
       </c>
       <c r="H788" t="n">
         <v>6468</v>
@@ -23250,7 +23250,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>14.8966732025146</v>
+        <v>14.896674156189</v>
       </c>
       <c r="H789" t="n">
         <v>6740</v>
@@ -23279,7 +23279,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>14.8236503601074</v>
+        <v>14.8236494064331</v>
       </c>
       <c r="H790" t="n">
         <v>3767</v>
@@ -23308,7 +23308,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>14.677604675293</v>
+        <v>14.6776056289673</v>
       </c>
       <c r="H791" t="n">
         <v>8705</v>
@@ -23366,7 +23366,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G793" t="n">
-        <v>14.5461664199829</v>
+        <v>14.54616355896</v>
       </c>
       <c r="H793" t="n">
         <v>7923</v>
@@ -23395,7 +23395,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G794" t="n">
-        <v>14.5461664199829</v>
+        <v>14.54616355896</v>
       </c>
       <c r="H794" t="n">
         <v>12332</v>
@@ -23453,7 +23453,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G796" t="n">
-        <v>14.5607690811157</v>
+        <v>14.5607681274414</v>
       </c>
       <c r="H796" t="n">
         <v>7876</v>
@@ -23482,7 +23482,7 @@
         <v>20.25</v>
       </c>
       <c r="G797" t="n">
-        <v>14.7871408462524</v>
+        <v>14.7871379852295</v>
       </c>
       <c r="H797" t="n">
         <v>5439</v>
@@ -23569,7 +23569,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G800" t="n">
-        <v>14.677604675293</v>
+        <v>14.6776056289673</v>
       </c>
       <c r="H800" t="n">
         <v>1489</v>
@@ -23598,7 +23598,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>14.7141141891479</v>
+        <v>14.7141170501709</v>
       </c>
       <c r="H801" t="n">
         <v>2452</v>
@@ -23656,7 +23656,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>14.7141141891479</v>
+        <v>14.7141170501709</v>
       </c>
       <c r="H803" t="n">
         <v>3235</v>
@@ -23685,7 +23685,7 @@
         <v>20.25</v>
       </c>
       <c r="G804" t="n">
-        <v>14.7871408462524</v>
+        <v>14.7871379852295</v>
       </c>
       <c r="H804" t="n">
         <v>2333</v>
@@ -23714,7 +23714,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G805" t="n">
-        <v>14.860161781311</v>
+        <v>14.8601608276367</v>
       </c>
       <c r="H805" t="n">
         <v>4289</v>
@@ -23743,7 +23743,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>14.9331846237183</v>
+        <v>14.9331865310669</v>
       </c>
       <c r="H806" t="n">
         <v>2520</v>
@@ -23772,7 +23772,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G807" t="n">
-        <v>15.0427188873291</v>
+        <v>15.0427207946777</v>
       </c>
       <c r="H807" t="n">
         <v>1542</v>
@@ -23801,7 +23801,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>15.0427188873291</v>
+        <v>15.0427207946777</v>
       </c>
       <c r="H808" t="n">
         <v>3076</v>
@@ -23859,7 +23859,7 @@
         <v>20.5</v>
       </c>
       <c r="G810" t="n">
-        <v>14.9696950912476</v>
+        <v>14.9696960449219</v>
       </c>
       <c r="H810" t="n">
         <v>6055</v>
@@ -23917,7 +23917,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>14.7141141891479</v>
+        <v>14.7141170501709</v>
       </c>
       <c r="H812" t="n">
         <v>4203</v>
@@ -23975,7 +23975,7 @@
         <v>20.25</v>
       </c>
       <c r="G814" t="n">
-        <v>14.7871408462524</v>
+        <v>14.7871379852295</v>
       </c>
       <c r="H814" t="n">
         <v>9203</v>
@@ -24004,7 +24004,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>14.677604675293</v>
+        <v>14.6776056289673</v>
       </c>
       <c r="H815" t="n">
         <v>10677</v>
@@ -24062,7 +24062,7 @@
         <v>20.25</v>
       </c>
       <c r="G817" t="n">
-        <v>14.7871408462524</v>
+        <v>14.7871379852295</v>
       </c>
       <c r="H817" t="n">
         <v>7125</v>
@@ -24091,7 +24091,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>14.8966732025146</v>
+        <v>14.896674156189</v>
       </c>
       <c r="H818" t="n">
         <v>3135</v>
@@ -24120,7 +24120,7 @@
         <v>21</v>
       </c>
       <c r="G819" t="n">
-        <v>15.3348121643066</v>
+        <v>15.334810256958</v>
       </c>
       <c r="H819" t="n">
         <v>19632</v>
@@ -24149,7 +24149,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>15.5903930664062</v>
+        <v>15.5903911590576</v>
       </c>
       <c r="H820" t="n">
         <v>10695</v>
@@ -24236,7 +24236,7 @@
         <v>22</v>
       </c>
       <c r="G823" t="n">
-        <v>16.0650405883789</v>
+        <v>16.0650386810303</v>
       </c>
       <c r="H823" t="n">
         <v>10428</v>
@@ -24294,7 +24294,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>15.9189920425415</v>
+        <v>15.9189939498901</v>
       </c>
       <c r="H825" t="n">
         <v>7491</v>
@@ -24352,7 +24352,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>15.9189920425415</v>
+        <v>15.9189939498901</v>
       </c>
       <c r="H827" t="n">
         <v>9863</v>
@@ -24410,7 +24410,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>15.9189920425415</v>
+        <v>15.9189939498901</v>
       </c>
       <c r="H829" t="n">
         <v>6136</v>
@@ -24439,7 +24439,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>15.9555053710938</v>
+        <v>15.9555072784424</v>
       </c>
       <c r="H830" t="n">
         <v>6690</v>
@@ -24497,7 +24497,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>15.9555053710938</v>
+        <v>15.9555072784424</v>
       </c>
       <c r="H832" t="n">
         <v>4840</v>
@@ -24526,7 +24526,7 @@
         <v>22</v>
       </c>
       <c r="G833" t="n">
-        <v>16.0650405883789</v>
+        <v>16.0650386810303</v>
       </c>
       <c r="H833" t="n">
         <v>14874</v>
@@ -24555,7 +24555,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G834" t="n">
-        <v>16.3206195831299</v>
+        <v>16.3206214904785</v>
       </c>
       <c r="H834" t="n">
         <v>25616</v>
@@ -24584,7 +24584,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>16.3571300506592</v>
+        <v>16.3571319580078</v>
       </c>
       <c r="H835" t="n">
         <v>6539</v>
@@ -24642,7 +24642,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G837" t="n">
-        <v>16.3571300506592</v>
+        <v>16.3571319580078</v>
       </c>
       <c r="H837" t="n">
         <v>6600</v>
@@ -24700,7 +24700,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G839" t="n">
-        <v>16.3571300506592</v>
+        <v>16.3571319580078</v>
       </c>
       <c r="H839" t="n">
         <v>5893</v>
@@ -24729,7 +24729,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>16.5762023925781</v>
+        <v>16.5762004852295</v>
       </c>
       <c r="H840" t="n">
         <v>4040</v>
@@ -24816,7 +24816,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>16.6492214202881</v>
+        <v>16.6492233276367</v>
       </c>
       <c r="H843" t="n">
         <v>4611</v>
@@ -24845,7 +24845,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G844" t="n">
-        <v>16.5762023925781</v>
+        <v>16.5762004852295</v>
       </c>
       <c r="H844" t="n">
         <v>5424</v>
@@ -24874,7 +24874,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G845" t="n">
-        <v>17.0143356323242</v>
+        <v>17.0143375396729</v>
       </c>
       <c r="H845" t="n">
         <v>9983</v>
@@ -24932,7 +24932,7 @@
         <v>23.5</v>
       </c>
       <c r="G847" t="n">
-        <v>17.1603832244873</v>
+        <v>17.16037940979</v>
       </c>
       <c r="H847" t="n">
         <v>19780</v>
@@ -24990,7 +24990,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>17.350212097168</v>
+        <v>17.3502101898193</v>
       </c>
       <c r="H849" t="n">
         <v>12110</v>
@@ -25019,7 +25019,7 @@
         <v>21.5</v>
       </c>
       <c r="G850" t="n">
-        <v>16.3251457214355</v>
+        <v>16.3251438140869</v>
       </c>
       <c r="H850" t="n">
         <v>14820</v>
@@ -25077,7 +25077,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>16.0214195251465</v>
+        <v>16.0214233398438</v>
       </c>
       <c r="H852" t="n">
         <v>7888</v>
@@ -25106,7 +25106,7 @@
         <v>20.75</v>
       </c>
       <c r="G853" t="n">
-        <v>15.7556638717651</v>
+        <v>15.7556619644165</v>
       </c>
       <c r="H853" t="n">
         <v>4049</v>
@@ -25135,7 +25135,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>15.3380432128906</v>
+        <v>15.338041305542</v>
       </c>
       <c r="H854" t="n">
         <v>14794</v>
@@ -25164,7 +25164,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.3000745773315</v>
+        <v>15.3000764846802</v>
       </c>
       <c r="H855" t="n">
         <v>6684</v>
@@ -25193,7 +25193,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G856" t="n">
-        <v>14.7305955886841</v>
+        <v>14.7305936813354</v>
       </c>
       <c r="H856" t="n">
         <v>17593</v>
@@ -25222,7 +25222,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G857" t="n">
-        <v>14.9432010650635</v>
+        <v>14.9432020187378</v>
       </c>
       <c r="H857" t="n">
         <v>25086</v>
@@ -25251,7 +25251,7 @@
         <v>20.25</v>
       </c>
       <c r="G858" t="n">
-        <v>15.3760108947754</v>
+        <v>15.3760070800781</v>
       </c>
       <c r="H858" t="n">
         <v>12074</v>
@@ -25280,7 +25280,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G859" t="n">
-        <v>15.262110710144</v>
+        <v>15.2621126174927</v>
       </c>
       <c r="H859" t="n">
         <v>12797</v>
@@ -25309,7 +25309,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>15.3000745773315</v>
+        <v>15.3000764846802</v>
       </c>
       <c r="H860" t="n">
         <v>1452</v>
@@ -25338,7 +25338,7 @@
         <v>20</v>
       </c>
       <c r="G861" t="n">
-        <v>15.1861791610718</v>
+        <v>15.1861810684204</v>
       </c>
       <c r="H861" t="n">
         <v>422</v>
@@ -25367,7 +25367,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G862" t="n">
-        <v>15.3380432128906</v>
+        <v>15.338041305542</v>
       </c>
       <c r="H862" t="n">
         <v>7527</v>
@@ -25396,7 +25396,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>15.4139738082886</v>
+        <v>15.4139719009399</v>
       </c>
       <c r="H863" t="n">
         <v>4932</v>
@@ -25425,7 +25425,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G864" t="n">
-        <v>15.3000745773315</v>
+        <v>15.3000764846802</v>
       </c>
       <c r="H864" t="n">
         <v>2103</v>
@@ -25454,7 +25454,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>15.3000745773315</v>
+        <v>15.3000764846802</v>
       </c>
       <c r="H865" t="n">
         <v>6460</v>
@@ -25483,7 +25483,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G866" t="n">
-        <v>14.9735727310181</v>
+        <v>14.973575592041</v>
       </c>
       <c r="H866" t="n">
         <v>8523</v>
@@ -25512,7 +25512,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G867" t="n">
-        <v>14.9432010650635</v>
+        <v>14.9432020187378</v>
       </c>
       <c r="H867" t="n">
         <v>2366</v>
@@ -25541,7 +25541,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G868" t="n">
-        <v>14.7002248764038</v>
+        <v>14.7002229690552</v>
       </c>
       <c r="H868" t="n">
         <v>3664</v>
@@ -25599,7 +25599,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>15.262110710144</v>
+        <v>15.2621126174927</v>
       </c>
       <c r="H870" t="n">
         <v>7157</v>
@@ -25628,7 +25628,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>15.3380432128906</v>
+        <v>15.338041305542</v>
       </c>
       <c r="H871" t="n">
         <v>2002</v>
@@ -25657,7 +25657,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G872" t="n">
-        <v>15.0950622558594</v>
+        <v>15.095064163208</v>
       </c>
       <c r="H872" t="n">
         <v>4868</v>
@@ -25686,7 +25686,7 @@
         <v>20</v>
       </c>
       <c r="G873" t="n">
-        <v>15.1861791610718</v>
+        <v>15.1861810684204</v>
       </c>
       <c r="H873" t="n">
         <v>3799</v>
@@ -25744,7 +25744,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G875" t="n">
-        <v>15.4139738082886</v>
+        <v>15.4139719009399</v>
       </c>
       <c r="H875" t="n">
         <v>1894</v>
@@ -25802,7 +25802,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>15.262110710144</v>
+        <v>15.2621126174927</v>
       </c>
       <c r="H877" t="n">
         <v>177</v>
@@ -25831,7 +25831,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G878" t="n">
-        <v>15.3380432128906</v>
+        <v>15.338041305542</v>
       </c>
       <c r="H878" t="n">
         <v>4001</v>
@@ -25860,7 +25860,7 @@
         <v>20.25</v>
       </c>
       <c r="G879" t="n">
-        <v>15.3760108947754</v>
+        <v>15.3760070800781</v>
       </c>
       <c r="H879" t="n">
         <v>4080</v>
@@ -25889,7 +25889,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>15.4139738082886</v>
+        <v>15.4139719009399</v>
       </c>
       <c r="H880" t="n">
         <v>428</v>
@@ -25918,7 +25918,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G881" t="n">
-        <v>15.4139738082886</v>
+        <v>15.4139719009399</v>
       </c>
       <c r="H881" t="n">
         <v>8219</v>
@@ -26005,7 +26005,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G884" t="n">
-        <v>15.0039463043213</v>
+        <v>15.0039472579956</v>
       </c>
       <c r="H884" t="n">
         <v>3246</v>
@@ -26034,7 +26034,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>14.9583873748779</v>
+        <v>14.9583892822266</v>
       </c>
       <c r="H885" t="n">
         <v>2696</v>
@@ -26063,7 +26063,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G886" t="n">
-        <v>15.262110710144</v>
+        <v>15.2621126174927</v>
       </c>
       <c r="H886" t="n">
         <v>2820</v>
@@ -26092,7 +26092,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>15.4139738082886</v>
+        <v>15.4139719009399</v>
       </c>
       <c r="H887" t="n">
         <v>2451</v>
@@ -26121,7 +26121,7 @@
         <v>20.25</v>
       </c>
       <c r="G888" t="n">
-        <v>15.3760108947754</v>
+        <v>15.3760070800781</v>
       </c>
       <c r="H888" t="n">
         <v>1472</v>
@@ -26150,7 +26150,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>15.5278692245483</v>
+        <v>15.527871131897</v>
       </c>
       <c r="H889" t="n">
         <v>2006</v>
@@ -26179,7 +26179,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G890" t="n">
-        <v>15.6797294616699</v>
+        <v>15.6797313690186</v>
       </c>
       <c r="H890" t="n">
         <v>223622</v>
@@ -26237,7 +26237,7 @@
         <v>20.5</v>
       </c>
       <c r="G892" t="n">
-        <v>15.5658340454102</v>
+        <v>15.5658359527588</v>
       </c>
       <c r="H892" t="n">
         <v>4077</v>
@@ -26266,7 +26266,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>15.3000745773315</v>
+        <v>15.3000764846802</v>
       </c>
       <c r="H893" t="n">
         <v>3182</v>
@@ -26295,7 +26295,7 @@
         <v>20.25</v>
       </c>
       <c r="G894" t="n">
-        <v>15.3760108947754</v>
+        <v>15.3760070800781</v>
       </c>
       <c r="H894" t="n">
         <v>2343</v>
@@ -26353,7 +26353,7 @@
         <v>20.25</v>
       </c>
       <c r="G896" t="n">
-        <v>15.3760108947754</v>
+        <v>15.3760070800781</v>
       </c>
       <c r="H896" t="n">
         <v>5235</v>
@@ -26440,7 +26440,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G899" t="n">
-        <v>15.4139738082886</v>
+        <v>15.4139719009399</v>
       </c>
       <c r="H899" t="n">
         <v>3234</v>
@@ -26469,7 +26469,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>15.4139738082886</v>
+        <v>15.4139719009399</v>
       </c>
       <c r="H900" t="n">
         <v>3009</v>
@@ -26498,7 +26498,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>15.3000745773315</v>
+        <v>15.3000764846802</v>
       </c>
       <c r="H901" t="n">
         <v>7880</v>
@@ -26527,7 +26527,7 @@
         <v>20.25</v>
       </c>
       <c r="G902" t="n">
-        <v>15.3760108947754</v>
+        <v>15.3760070800781</v>
       </c>
       <c r="H902" t="n">
         <v>3939</v>
@@ -26585,7 +26585,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>15.983452796936</v>
+        <v>15.9834547042847</v>
       </c>
       <c r="H904" t="n">
         <v>11690</v>
@@ -26643,7 +26643,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G906" t="n">
-        <v>16.6668319702148</v>
+        <v>16.6668338775635</v>
       </c>
       <c r="H906" t="n">
         <v>4931</v>
@@ -26672,7 +26672,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G907" t="n">
-        <v>16.5529365539551</v>
+        <v>16.5529384613037</v>
       </c>
       <c r="H907" t="n">
         <v>3269</v>
@@ -26701,7 +26701,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G908" t="n">
-        <v>16.5529365539551</v>
+        <v>16.5529384613037</v>
       </c>
       <c r="H908" t="n">
         <v>1580</v>
@@ -26759,7 +26759,7 @@
         <v>21.25</v>
       </c>
       <c r="G910" t="n">
-        <v>16.1353130340576</v>
+        <v>16.1353168487549</v>
       </c>
       <c r="H910" t="n">
         <v>3446</v>
@@ -26788,7 +26788,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G911" t="n">
-        <v>16.2112503051758</v>
+        <v>16.2112483978271</v>
       </c>
       <c r="H911" t="n">
         <v>3708</v>
@@ -26817,7 +26817,7 @@
         <v>21.5</v>
       </c>
       <c r="G912" t="n">
-        <v>16.3251457214355</v>
+        <v>16.3251438140869</v>
       </c>
       <c r="H912" t="n">
         <v>9079</v>
@@ -26846,7 +26846,7 @@
         <v>21.5</v>
       </c>
       <c r="G913" t="n">
-        <v>16.3251457214355</v>
+        <v>16.3251438140869</v>
       </c>
       <c r="H913" t="n">
         <v>1062</v>
@@ -26875,7 +26875,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G914" t="n">
-        <v>15.983452796936</v>
+        <v>15.9834547042847</v>
       </c>
       <c r="H914" t="n">
         <v>1402</v>
@@ -26904,7 +26904,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>16.0214195251465</v>
+        <v>16.0214233398438</v>
       </c>
       <c r="H915" t="n">
         <v>1082</v>
@@ -26933,7 +26933,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>15.7176990509033</v>
+        <v>15.7176952362061</v>
       </c>
       <c r="H916" t="n">
         <v>911</v>
@@ -26991,7 +26991,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>15.7936267852783</v>
+        <v>15.793625831604</v>
       </c>
       <c r="H918" t="n">
         <v>8919</v>
@@ -27020,7 +27020,7 @@
         <v>21</v>
       </c>
       <c r="G919" t="n">
-        <v>15.9454879760742</v>
+        <v>15.9454898834229</v>
       </c>
       <c r="H919" t="n">
         <v>523</v>
@@ -27078,7 +27078,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>15.6797294616699</v>
+        <v>15.6797313690186</v>
       </c>
       <c r="H921" t="n">
         <v>1350</v>
@@ -27136,7 +27136,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G923" t="n">
-        <v>15.6417646408081</v>
+        <v>15.6417684555054</v>
       </c>
       <c r="H923" t="n">
         <v>1326</v>
@@ -27194,7 +27194,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G925" t="n">
-        <v>15.3380432128906</v>
+        <v>15.338041305542</v>
       </c>
       <c r="H925" t="n">
         <v>11846</v>
@@ -27223,7 +27223,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.262110710144</v>
+        <v>15.2621126174927</v>
       </c>
       <c r="H926" t="n">
         <v>7179</v>
@@ -27252,7 +27252,7 @@
         <v>20</v>
       </c>
       <c r="G927" t="n">
-        <v>15.1861791610718</v>
+        <v>15.1861810684204</v>
       </c>
       <c r="H927" t="n">
         <v>1158</v>
@@ -27310,7 +27310,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G929" t="n">
-        <v>15.4139738082886</v>
+        <v>15.4139719009399</v>
       </c>
       <c r="H929" t="n">
         <v>993</v>
@@ -27368,7 +27368,7 @@
         <v>20</v>
       </c>
       <c r="G931" t="n">
-        <v>15.1861791610718</v>
+        <v>15.1861810684204</v>
       </c>
       <c r="H931" t="n">
         <v>827</v>
@@ -27397,7 +27397,7 @@
         <v>20</v>
       </c>
       <c r="G932" t="n">
-        <v>15.1861791610718</v>
+        <v>15.1861810684204</v>
       </c>
       <c r="H932" t="n">
         <v>1475</v>
@@ -27426,7 +27426,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>15.7936267852783</v>
+        <v>15.793625831604</v>
       </c>
       <c r="H933" t="n">
         <v>3402</v>
@@ -27455,7 +27455,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G934" t="n">
-        <v>15.6797294616699</v>
+        <v>15.6797313690186</v>
       </c>
       <c r="H934" t="n">
         <v>1493</v>
@@ -27484,7 +27484,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G935" t="n">
-        <v>15.5278692245483</v>
+        <v>15.527871131897</v>
       </c>
       <c r="H935" t="n">
         <v>1179</v>
@@ -27513,7 +27513,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G936" t="n">
-        <v>15.983452796936</v>
+        <v>15.9834547042847</v>
       </c>
       <c r="H936" t="n">
         <v>8102</v>
@@ -27542,7 +27542,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G937" t="n">
-        <v>15.8695592880249</v>
+        <v>15.8695573806763</v>
       </c>
       <c r="H937" t="n">
         <v>4816</v>
@@ -27600,7 +27600,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>15.983452796936</v>
+        <v>15.9834547042847</v>
       </c>
       <c r="H939" t="n">
         <v>706</v>
@@ -27629,7 +27629,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G940" t="n">
-        <v>16.097354888916</v>
+        <v>16.0973529815674</v>
       </c>
       <c r="H940" t="n">
         <v>3395</v>
@@ -27658,7 +27658,7 @@
         <v>21.25</v>
       </c>
       <c r="G941" t="n">
-        <v>16.1353130340576</v>
+        <v>16.1353168487549</v>
       </c>
       <c r="H941" t="n">
         <v>7999</v>
@@ -27687,7 +27687,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>16.2112503051758</v>
+        <v>16.2112483978271</v>
       </c>
       <c r="H942" t="n">
         <v>6454</v>
@@ -27803,7 +27803,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>16.173282623291</v>
+        <v>16.1732807159424</v>
       </c>
       <c r="H946" t="n">
         <v>3633</v>
@@ -27832,7 +27832,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>16.2112503051758</v>
+        <v>16.2112483978271</v>
       </c>
       <c r="H947" t="n">
         <v>897</v>
@@ -27890,7 +27890,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G949" t="n">
-        <v>16.173282623291</v>
+        <v>16.1732807159424</v>
       </c>
       <c r="H949" t="n">
         <v>5914</v>
@@ -27919,7 +27919,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>16.0214195251465</v>
+        <v>16.0214233398438</v>
       </c>
       <c r="H950" t="n">
         <v>2150</v>
@@ -27977,7 +27977,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G952" t="n">
-        <v>16.097354888916</v>
+        <v>16.0973529815674</v>
       </c>
       <c r="H952" t="n">
         <v>1293</v>
@@ -28006,7 +28006,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G953" t="n">
-        <v>16.2112503051758</v>
+        <v>16.2112483978271</v>
       </c>
       <c r="H953" t="n">
         <v>951</v>
@@ -28035,7 +28035,7 @@
         <v>21.25</v>
       </c>
       <c r="G954" t="n">
-        <v>16.1353130340576</v>
+        <v>16.1353168487549</v>
       </c>
       <c r="H954" t="n">
         <v>926</v>
@@ -28180,7 +28180,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G959" t="n">
-        <v>16.097354888916</v>
+        <v>16.0973529815674</v>
       </c>
       <c r="H959" t="n">
         <v>1275</v>
@@ -28238,7 +28238,7 @@
         <v>21.25</v>
       </c>
       <c r="G961" t="n">
-        <v>16.1353130340576</v>
+        <v>16.1353168487549</v>
       </c>
       <c r="H961" t="n">
         <v>1316</v>
@@ -28267,7 +28267,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G962" t="n">
-        <v>16.2112503051758</v>
+        <v>16.2112483978271</v>
       </c>
       <c r="H962" t="n">
         <v>1807</v>
@@ -28296,7 +28296,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>16.4770069122314</v>
+        <v>16.4770050048828</v>
       </c>
       <c r="H963" t="n">
         <v>1425</v>
@@ -28354,7 +28354,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>16.4770069122314</v>
+        <v>16.4770050048828</v>
       </c>
       <c r="H965" t="n">
         <v>668</v>
@@ -28383,7 +28383,7 @@
         <v>21.5</v>
       </c>
       <c r="G966" t="n">
-        <v>16.3251457214355</v>
+        <v>16.3251438140869</v>
       </c>
       <c r="H966" t="n">
         <v>792</v>
@@ -28441,7 +28441,7 @@
         <v>21.25</v>
       </c>
       <c r="G968" t="n">
-        <v>16.1353130340576</v>
+        <v>16.1353168487549</v>
       </c>
       <c r="H968" t="n">
         <v>1182</v>
@@ -28499,7 +28499,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G970" t="n">
-        <v>16.4770069122314</v>
+        <v>16.4770050048828</v>
       </c>
       <c r="H970" t="n">
         <v>725</v>
@@ -28528,7 +28528,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G971" t="n">
-        <v>16.5529365539551</v>
+        <v>16.5529384613037</v>
       </c>
       <c r="H971" t="n">
         <v>40087</v>
@@ -28557,7 +28557,7 @@
         <v>21.5</v>
       </c>
       <c r="G972" t="n">
-        <v>16.3251457214355</v>
+        <v>16.3251438140869</v>
       </c>
       <c r="H972" t="n">
         <v>1660</v>
@@ -28615,7 +28615,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>16.173282623291</v>
+        <v>16.1732807159424</v>
       </c>
       <c r="H974" t="n">
         <v>746</v>
@@ -28644,7 +28644,7 @@
         <v>21</v>
       </c>
       <c r="G975" t="n">
-        <v>15.9454879760742</v>
+        <v>15.9454898834229</v>
       </c>
       <c r="H975" t="n">
         <v>5008</v>
@@ -28673,7 +28673,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>16.2112503051758</v>
+        <v>16.2112483978271</v>
       </c>
       <c r="H976" t="n">
         <v>9959</v>
@@ -28731,7 +28731,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>16.173282623291</v>
+        <v>16.1732807159424</v>
       </c>
       <c r="H978" t="n">
         <v>7468</v>
@@ -28760,7 +28760,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G979" t="n">
-        <v>16.4770069122314</v>
+        <v>16.4770050048828</v>
       </c>
       <c r="H979" t="n">
         <v>6506</v>
@@ -28818,7 +28818,7 @@
         <v>23</v>
       </c>
       <c r="G981" t="n">
-        <v>17.4641094207764</v>
+        <v>17.4641075134277</v>
       </c>
       <c r="H981" t="n">
         <v>32356</v>
@@ -28905,7 +28905,7 @@
         <v>24</v>
       </c>
       <c r="G984" t="n">
-        <v>18.2234153747559</v>
+        <v>18.2234134674072</v>
       </c>
       <c r="H984" t="n">
         <v>26053</v>
@@ -28963,7 +28963,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>17.8817272186279</v>
+        <v>17.8817253112793</v>
       </c>
       <c r="H986" t="n">
         <v>8521</v>
@@ -28992,7 +28992,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>18.451208114624</v>
+        <v>18.4512100219727</v>
       </c>
       <c r="H987" t="n">
         <v>11916</v>
@@ -29021,7 +29021,7 @@
         <v>24</v>
       </c>
       <c r="G988" t="n">
-        <v>18.2234153747559</v>
+        <v>18.2234134674072</v>
       </c>
       <c r="H988" t="n">
         <v>15758</v>
@@ -29050,7 +29050,7 @@
         <v>24</v>
       </c>
       <c r="G989" t="n">
-        <v>18.2234153747559</v>
+        <v>18.2234134674072</v>
       </c>
       <c r="H989" t="n">
         <v>2124</v>
@@ -29079,7 +29079,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G990" t="n">
-        <v>18.1474876403809</v>
+        <v>18.1474857330322</v>
       </c>
       <c r="H990" t="n">
         <v>11697</v>
@@ -29108,7 +29108,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>17.6918983459473</v>
+        <v>17.6919002532959</v>
       </c>
       <c r="H991" t="n">
         <v>1764</v>
@@ -29166,7 +29166,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G993" t="n">
-        <v>18.375280380249</v>
+        <v>18.3752784729004</v>
       </c>
       <c r="H993" t="n">
         <v>5146</v>
@@ -29253,7 +29253,7 @@
         <v>24.5</v>
       </c>
       <c r="G996" t="n">
-        <v>18.6030712127686</v>
+        <v>18.6030693054199</v>
       </c>
       <c r="H996" t="n">
         <v>8561</v>
@@ -29340,7 +29340,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G999" t="n">
-        <v>17.8817272186279</v>
+        <v>17.8817253112793</v>
       </c>
       <c r="H999" t="n">
         <v>4163</v>
@@ -29369,7 +29369,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1000" t="n">
-        <v>17.7678298950195</v>
+        <v>17.7678318023682</v>
       </c>
       <c r="H1000" t="n">
         <v>2615</v>
@@ -29398,7 +29398,7 @@
         <v>23.25</v>
       </c>
       <c r="G1001" t="n">
-        <v>17.6539363861084</v>
+        <v>17.6539344787598</v>
       </c>
       <c r="H1001" t="n">
         <v>1954</v>
@@ -29427,7 +29427,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1002" t="n">
-        <v>17.8817272186279</v>
+        <v>17.8817253112793</v>
       </c>
       <c r="H1002" t="n">
         <v>2272</v>
@@ -29456,7 +29456,7 @@
         <v>23.5</v>
       </c>
       <c r="G1003" t="n">
-        <v>17.8437614440918</v>
+        <v>17.8437595367432</v>
       </c>
       <c r="H1003" t="n">
         <v>1415</v>
@@ -29514,7 +29514,7 @@
         <v>23.75</v>
       </c>
       <c r="G1005" t="n">
-        <v>18.0335865020752</v>
+        <v>18.0335903167725</v>
       </c>
       <c r="H1005" t="n">
         <v>2227</v>
@@ -29543,7 +29543,7 @@
         <v>23.75</v>
       </c>
       <c r="G1006" t="n">
-        <v>18.0335865020752</v>
+        <v>18.0335903167725</v>
       </c>
       <c r="H1006" t="n">
         <v>1262</v>
@@ -29572,7 +29572,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1007" t="n">
-        <v>17.7678298950195</v>
+        <v>17.7678318023682</v>
       </c>
       <c r="H1007" t="n">
         <v>4748</v>
@@ -29601,7 +29601,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1008" t="n">
-        <v>18.1095218658447</v>
+        <v>18.1095199584961</v>
       </c>
       <c r="H1008" t="n">
         <v>2166</v>
@@ -29688,7 +29688,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.3122444152832</v>
+        <v>17.3122463226318</v>
       </c>
       <c r="H1011" t="n">
         <v>2380</v>
@@ -29717,7 +29717,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>17.350212097168</v>
+        <v>17.3502101898193</v>
       </c>
       <c r="H1012" t="n">
         <v>2954</v>
@@ -29804,7 +29804,7 @@
         <v>24</v>
       </c>
       <c r="G1015" t="n">
-        <v>18.2234153747559</v>
+        <v>18.2234134674072</v>
       </c>
       <c r="H1015" t="n">
         <v>1462</v>
@@ -29833,7 +29833,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1016" t="n">
-        <v>17.9956226348877</v>
+        <v>17.995626449585</v>
       </c>
       <c r="H1016" t="n">
         <v>4823</v>
@@ -29862,7 +29862,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1017" t="n">
-        <v>17.8817272186279</v>
+        <v>17.8817253112793</v>
       </c>
       <c r="H1017" t="n">
         <v>3362</v>
@@ -29891,7 +29891,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>17.9956226348877</v>
+        <v>17.995626449585</v>
       </c>
       <c r="H1018" t="n">
         <v>1226</v>
@@ -29949,7 +29949,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>17.7678298950195</v>
+        <v>17.7678318023682</v>
       </c>
       <c r="H1020" t="n">
         <v>2237</v>
@@ -29978,7 +29978,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1021" t="n">
-        <v>17.7678298950195</v>
+        <v>17.7678318023682</v>
       </c>
       <c r="H1021" t="n">
         <v>1517</v>
@@ -30036,7 +30036,7 @@
         <v>23.5</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.8437614440918</v>
+        <v>17.8437595367432</v>
       </c>
       <c r="H1023" t="n">
         <v>3587</v>
@@ -30065,7 +30065,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1024" t="n">
-        <v>18.1095218658447</v>
+        <v>18.1095199584961</v>
       </c>
       <c r="H1024" t="n">
         <v>240</v>
@@ -30181,7 +30181,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.5780029296875</v>
+        <v>17.5780067443848</v>
       </c>
       <c r="H1028" t="n">
         <v>956</v>
@@ -30210,7 +30210,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.5780029296875</v>
+        <v>17.5780067443848</v>
       </c>
       <c r="H1029" t="n">
         <v>186</v>
@@ -30297,7 +30297,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>17.5780029296875</v>
+        <v>17.5780067443848</v>
       </c>
       <c r="H1032" t="n">
         <v>363</v>
@@ -30326,7 +30326,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.2363166809082</v>
+        <v>17.2363147735596</v>
       </c>
       <c r="H1033" t="n">
         <v>1238</v>
@@ -30355,7 +30355,7 @@
         <v>22.75</v>
       </c>
       <c r="G1034" t="n">
-        <v>17.2742786407471</v>
+        <v>17.2742805480957</v>
       </c>
       <c r="H1034" t="n">
         <v>1601</v>
@@ -30384,7 +30384,7 @@
         <v>23.25</v>
       </c>
       <c r="G1035" t="n">
-        <v>17.6539363861084</v>
+        <v>17.6539344787598</v>
       </c>
       <c r="H1035" t="n">
         <v>7995</v>
@@ -30442,7 +30442,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1037" t="n">
-        <v>17.8817272186279</v>
+        <v>17.8817253112793</v>
       </c>
       <c r="H1037" t="n">
         <v>4186</v>
@@ -30500,7 +30500,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>17.5780029296875</v>
+        <v>17.5780067443848</v>
       </c>
       <c r="H1039" t="n">
         <v>971</v>
@@ -30529,7 +30529,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>17.5780029296875</v>
+        <v>17.5780067443848</v>
       </c>
       <c r="H1040" t="n">
         <v>35</v>
@@ -30558,7 +30558,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>17.7678298950195</v>
+        <v>17.7678318023682</v>
       </c>
       <c r="H1041" t="n">
         <v>533</v>
@@ -30587,7 +30587,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1042" t="n">
-        <v>17.9956226348877</v>
+        <v>17.995626449585</v>
       </c>
       <c r="H1042" t="n">
         <v>4752</v>
@@ -30616,7 +30616,7 @@
         <v>23.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>18.0335865020752</v>
+        <v>18.0335903167725</v>
       </c>
       <c r="H1043" t="n">
         <v>5100</v>
@@ -30645,7 +30645,7 @@
         <v>23.75</v>
       </c>
       <c r="G1044" t="n">
-        <v>18.0335865020752</v>
+        <v>18.0335903167725</v>
       </c>
       <c r="H1044" t="n">
         <v>498</v>
@@ -30703,7 +30703,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1046" t="n">
-        <v>17.7678298950195</v>
+        <v>17.7678318023682</v>
       </c>
       <c r="H1046" t="n">
         <v>3295</v>
@@ -30732,7 +30732,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1047" t="n">
-        <v>17.6918983459473</v>
+        <v>17.6919002532959</v>
       </c>
       <c r="H1047" t="n">
         <v>4011</v>
@@ -30761,7 +30761,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>17.6918983459473</v>
+        <v>17.6919002532959</v>
       </c>
       <c r="H1048" t="n">
         <v>1087</v>
@@ -30790,7 +30790,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1049" t="n">
-        <v>17.5780029296875</v>
+        <v>17.5780067443848</v>
       </c>
       <c r="H1049" t="n">
         <v>741</v>
@@ -30819,7 +30819,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1050" t="n">
-        <v>17.5780029296875</v>
+        <v>17.5780067443848</v>
       </c>
       <c r="H1050" t="n">
         <v>1658</v>
@@ -30848,7 +30848,7 @@
         <v>23.25</v>
       </c>
       <c r="G1051" t="n">
-        <v>17.6539363861084</v>
+        <v>17.6539344787598</v>
       </c>
       <c r="H1051" t="n">
         <v>933</v>
@@ -30906,7 +30906,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1053" t="n">
-        <v>15.8695592880249</v>
+        <v>15.8695573806763</v>
       </c>
       <c r="H1053" t="n">
         <v>20383</v>
@@ -30935,7 +30935,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>16.7807331085205</v>
+        <v>16.7807292938232</v>
       </c>
       <c r="H1054" t="n">
         <v>4741</v>
@@ -31022,7 +31022,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1057" t="n">
-        <v>16.7807331085205</v>
+        <v>16.7807292938232</v>
       </c>
       <c r="H1057" t="n">
         <v>8056</v>
@@ -31051,7 +31051,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>15.8695592880249</v>
+        <v>15.8695573806763</v>
       </c>
       <c r="H1058" t="n">
         <v>6749</v>
@@ -31080,7 +31080,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>15.983452796936</v>
+        <v>15.9834547042847</v>
       </c>
       <c r="H1059" t="n">
         <v>4932</v>
@@ -31109,7 +31109,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>15.8695592880249</v>
+        <v>15.8695573806763</v>
       </c>
       <c r="H1060" t="n">
         <v>1481</v>
@@ -31138,7 +31138,7 @@
         <v>20.75</v>
       </c>
       <c r="G1061" t="n">
-        <v>15.7556638717651</v>
+        <v>15.7556619644165</v>
       </c>
       <c r="H1061" t="n">
         <v>4418</v>
@@ -31196,7 +31196,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1063" t="n">
-        <v>14.7305955886841</v>
+        <v>14.7305936813354</v>
       </c>
       <c r="H1063" t="n">
         <v>10094</v>
@@ -31225,7 +31225,7 @@
         <v>19.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>14.806526184082</v>
+        <v>14.8065242767334</v>
       </c>
       <c r="H1064" t="n">
         <v>3275</v>
@@ -31312,7 +31312,7 @@
         <v>18</v>
       </c>
       <c r="G1067" t="n">
-        <v>13.6675605773926</v>
+        <v>13.6675615310669</v>
       </c>
       <c r="H1067" t="n">
         <v>4732</v>
@@ -31428,7 +31428,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1071" t="n">
-        <v>12.8626937866211</v>
+        <v>12.8626956939697</v>
       </c>
       <c r="H1071" t="n">
         <v>4796</v>
@@ -31457,7 +31457,7 @@
         <v>17.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>13.2879066467285</v>
+        <v>13.2879095077515</v>
       </c>
       <c r="H1072" t="n">
         <v>1633</v>
@@ -31486,7 +31486,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>12.9841833114624</v>
+        <v>12.9841842651367</v>
       </c>
       <c r="H1073" t="n">
         <v>5036</v>
@@ -31515,7 +31515,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1074" t="n">
-        <v>12.8930673599243</v>
+        <v>12.89306640625</v>
       </c>
       <c r="H1074" t="n">
         <v>10218</v>
@@ -31544,7 +31544,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1075" t="n">
-        <v>12.8626937866211</v>
+        <v>12.8626956939697</v>
       </c>
       <c r="H1075" t="n">
         <v>10768</v>
@@ -31573,7 +31573,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.6804618835449</v>
+        <v>12.6804609298706</v>
       </c>
       <c r="H1076" t="n">
         <v>3455</v>
@@ -31631,7 +31631,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1078" t="n">
-        <v>11.5111236572266</v>
+        <v>11.5111255645752</v>
       </c>
       <c r="H1078" t="n">
         <v>11398</v>
@@ -31660,7 +31660,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1079" t="n">
-        <v>11.3137035369873</v>
+        <v>11.3137044906616</v>
       </c>
       <c r="H1079" t="n">
         <v>14513</v>
@@ -31689,7 +31689,7 @@
         <v>14</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.6303262710571</v>
+        <v>10.6303272247314</v>
       </c>
       <c r="H1080" t="n">
         <v>18855</v>
@@ -31747,7 +31747,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.0988101959229</v>
+        <v>10.0988111495972</v>
       </c>
       <c r="H1082" t="n">
         <v>9651</v>
@@ -31834,7 +31834,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1085" t="n">
-        <v>10.8960857391357</v>
+        <v>10.8960847854614</v>
       </c>
       <c r="H1085" t="n">
         <v>35594</v>
@@ -31863,7 +31863,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1086" t="n">
-        <v>11.5414962768555</v>
+        <v>11.5414972305298</v>
       </c>
       <c r="H1086" t="n">
         <v>39715</v>
@@ -31950,7 +31950,7 @@
         <v>15</v>
       </c>
       <c r="G1089" t="n">
-        <v>11.3896369934082</v>
+        <v>11.3896360397339</v>
       </c>
       <c r="H1089" t="n">
         <v>20362</v>
@@ -32066,7 +32066,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1093" t="n">
-        <v>11.2377738952637</v>
+        <v>11.2377729415894</v>
       </c>
       <c r="H1093" t="n">
         <v>13278</v>
@@ -32182,7 +32182,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1097" t="n">
-        <v>11.3516683578491</v>
+        <v>11.3516693115234</v>
       </c>
       <c r="H1097" t="n">
         <v>27987</v>
@@ -32211,7 +32211,7 @@
         <v>15</v>
       </c>
       <c r="G1098" t="n">
-        <v>11.3896369934082</v>
+        <v>11.3896360397339</v>
       </c>
       <c r="H1098" t="n">
         <v>37906</v>
@@ -32240,7 +32240,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1099" t="n">
-        <v>11.3516683578491</v>
+        <v>11.3516693115234</v>
       </c>
       <c r="H1099" t="n">
         <v>19505</v>
@@ -32298,7 +32298,7 @@
         <v>15</v>
       </c>
       <c r="G1101" t="n">
-        <v>11.3896369934082</v>
+        <v>11.3896360397339</v>
       </c>
       <c r="H1101" t="n">
         <v>4819</v>
@@ -32472,7 +32472,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1107" t="n">
-        <v>10.7442226409912</v>
+        <v>10.7442216873169</v>
       </c>
       <c r="H1107" t="n">
         <v>37661</v>
@@ -32588,7 +32588,7 @@
         <v>14</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.6303262710571</v>
+        <v>10.6303272247314</v>
       </c>
       <c r="H1111" t="n">
         <v>27604</v>
@@ -32617,7 +32617,7 @@
         <v>14</v>
       </c>
       <c r="G1112" t="n">
-        <v>10.6303262710571</v>
+        <v>10.6303272247314</v>
       </c>
       <c r="H1112" t="n">
         <v>40388</v>
@@ -32646,7 +32646,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="n">
-        <v>11.0099802017212</v>
+        <v>11.0099811553955</v>
       </c>
       <c r="H1113" t="n">
         <v>30556</v>
@@ -32704,7 +32704,7 @@
         <v>15</v>
       </c>
       <c r="G1115" t="n">
-        <v>11.3896369934082</v>
+        <v>11.3896360397339</v>
       </c>
       <c r="H1115" t="n">
         <v>69130</v>
@@ -32733,7 +32733,7 @@
         <v>15.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>11.9591178894043</v>
+        <v>11.95911693573</v>
       </c>
       <c r="H1116" t="n">
         <v>75995</v>
@@ -32791,7 +32791,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.9841833114624</v>
+        <v>12.9841842651367</v>
       </c>
       <c r="H1118" t="n">
         <v>97753</v>
@@ -32820,7 +32820,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>13.7814588546753</v>
+        <v>13.781457901001</v>
       </c>
       <c r="H1119" t="n">
         <v>119143</v>
@@ -32849,7 +32849,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1120" t="n">
-        <v>13.821403503418</v>
+        <v>13.8214044570923</v>
       </c>
       <c r="H1120" t="n">
         <v>51737</v>
@@ -32878,7 +32878,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>13.7415132522583</v>
+        <v>13.7415142059326</v>
       </c>
       <c r="H1121" t="n">
         <v>27596</v>
@@ -32907,7 +32907,7 @@
         <v>17</v>
       </c>
       <c r="G1122" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1122" t="n">
         <v>52406</v>
@@ -32936,7 +32936,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1123" t="n">
-        <v>13.5417814254761</v>
+        <v>13.5417804718018</v>
       </c>
       <c r="H1123" t="n">
         <v>18242</v>
@@ -32965,7 +32965,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>13.9012956619263</v>
+        <v>13.9012966156006</v>
       </c>
       <c r="H1124" t="n">
         <v>27598</v>
@@ -32994,7 +32994,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1125" t="n">
-        <v>14.3007583618164</v>
+        <v>14.300760269165</v>
       </c>
       <c r="H1125" t="n">
         <v>44339</v>
@@ -33023,7 +33023,7 @@
         <v>17.5</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.9811906814575</v>
+        <v>13.9811916351318</v>
       </c>
       <c r="H1126" t="n">
         <v>24929</v>
@@ -33052,7 +33052,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1127" t="n">
-        <v>13.5417814254761</v>
+        <v>13.5417804718018</v>
       </c>
       <c r="H1127" t="n">
         <v>12714</v>
@@ -33081,7 +33081,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>13.1423196792603</v>
+        <v>13.1423187255859</v>
       </c>
       <c r="H1128" t="n">
         <v>19454</v>
@@ -33168,7 +33168,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>13.4618892669678</v>
+        <v>13.4618883132935</v>
       </c>
       <c r="H1131" t="n">
         <v>27092</v>
@@ -33197,7 +33197,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1132" t="n">
-        <v>13.5417814254761</v>
+        <v>13.5417804718018</v>
       </c>
       <c r="H1132" t="n">
         <v>7137</v>
@@ -33255,7 +33255,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1134" t="n">
-        <v>13.9012956619263</v>
+        <v>13.9012966156006</v>
       </c>
       <c r="H1134" t="n">
         <v>13646</v>
@@ -33284,7 +33284,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1135" t="n">
-        <v>14.2208671569824</v>
+        <v>14.2208681106567</v>
       </c>
       <c r="H1135" t="n">
         <v>16341</v>
@@ -33371,7 +33371,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>14.0211343765259</v>
+        <v>14.0211353302002</v>
       </c>
       <c r="H1138" t="n">
         <v>8446</v>
@@ -33400,7 +33400,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1139" t="n">
-        <v>14.1010293960571</v>
+        <v>14.1010274887085</v>
       </c>
       <c r="H1139" t="n">
         <v>12638</v>
@@ -33429,7 +33429,7 @@
         <v>17.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>13.9811906814575</v>
+        <v>13.9811916351318</v>
       </c>
       <c r="H1140" t="n">
         <v>10167</v>
@@ -33458,7 +33458,7 @@
         <v>17</v>
       </c>
       <c r="G1141" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1141" t="n">
         <v>11908</v>
@@ -33487,7 +33487,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1142" t="n">
-        <v>13.3021030426025</v>
+        <v>13.3021039962769</v>
       </c>
       <c r="H1142" t="n">
         <v>12969</v>
@@ -33516,7 +33516,7 @@
         <v>16.5</v>
       </c>
       <c r="G1143" t="n">
-        <v>13.1822662353516</v>
+        <v>13.1822652816772</v>
       </c>
       <c r="H1143" t="n">
         <v>30779</v>
@@ -33603,7 +33603,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>13.6216745376587</v>
+        <v>13.6216735839844</v>
       </c>
       <c r="H1146" t="n">
         <v>13876</v>
@@ -33632,7 +33632,7 @@
         <v>17.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>13.9811906814575</v>
+        <v>13.9811916351318</v>
       </c>
       <c r="H1147" t="n">
         <v>9535</v>
@@ -33661,7 +33661,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1148" t="n">
-        <v>13.9412431716919</v>
+        <v>13.9412441253662</v>
       </c>
       <c r="H1148" t="n">
         <v>8605</v>
@@ -33719,7 +33719,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1150" t="n">
-        <v>14.0211343765259</v>
+        <v>14.0211353302002</v>
       </c>
       <c r="H1150" t="n">
         <v>9081</v>
@@ -33777,7 +33777,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>13.9012956619263</v>
+        <v>13.9012966156006</v>
       </c>
       <c r="H1152" t="n">
         <v>6090</v>
@@ -33806,7 +33806,7 @@
         <v>17.5</v>
       </c>
       <c r="G1153" t="n">
-        <v>13.9811906814575</v>
+        <v>13.9811916351318</v>
       </c>
       <c r="H1153" t="n">
         <v>1160</v>
@@ -33835,7 +33835,7 @@
         <v>17</v>
       </c>
       <c r="G1154" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1154" t="n">
         <v>10520</v>
@@ -33864,7 +33864,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1155" t="n">
-        <v>13.4618892669678</v>
+        <v>13.4618883132935</v>
       </c>
       <c r="H1155" t="n">
         <v>2236</v>
@@ -33893,7 +33893,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>13.821403503418</v>
+        <v>13.8214044570923</v>
       </c>
       <c r="H1156" t="n">
         <v>3186</v>
@@ -33922,7 +33922,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1157" t="n">
-        <v>13.4618892669678</v>
+        <v>13.4618883132935</v>
       </c>
       <c r="H1157" t="n">
         <v>6880</v>
@@ -33951,7 +33951,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1158" t="n">
-        <v>13.5417814254761</v>
+        <v>13.5417804718018</v>
       </c>
       <c r="H1158" t="n">
         <v>809</v>
@@ -33980,7 +33980,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>13.3021030426025</v>
+        <v>13.3021039962769</v>
       </c>
       <c r="H1159" t="n">
         <v>4842</v>
@@ -34038,7 +34038,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>13.1023721694946</v>
+        <v>13.1023712158203</v>
       </c>
       <c r="H1161" t="n">
         <v>8106</v>
@@ -34067,7 +34067,7 @@
         <v>16.5</v>
       </c>
       <c r="G1162" t="n">
-        <v>13.1822662353516</v>
+        <v>13.1822652816772</v>
       </c>
       <c r="H1162" t="n">
         <v>3020</v>
@@ -34096,7 +34096,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1163" t="n">
-        <v>12.942587852478</v>
+        <v>12.9425888061523</v>
       </c>
       <c r="H1163" t="n">
         <v>5792</v>
@@ -34125,7 +34125,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>12.942587852478</v>
+        <v>12.9425888061523</v>
       </c>
       <c r="H1164" t="n">
         <v>1692</v>
@@ -34154,7 +34154,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>13.3021030426025</v>
+        <v>13.3021039962769</v>
       </c>
       <c r="H1165" t="n">
         <v>4184</v>
@@ -34299,7 +34299,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.7415132522583</v>
+        <v>13.7415142059326</v>
       </c>
       <c r="H1170" t="n">
         <v>1674</v>
@@ -34328,7 +34328,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.7415132522583</v>
+        <v>13.7415142059326</v>
       </c>
       <c r="H1171" t="n">
         <v>810</v>
@@ -34357,7 +34357,7 @@
         <v>17</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1172" t="n">
         <v>1051</v>
@@ -34386,7 +34386,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.5417814254761</v>
+        <v>13.5417804718018</v>
       </c>
       <c r="H1173" t="n">
         <v>1123</v>
@@ -34415,7 +34415,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.5417814254761</v>
+        <v>13.5417804718018</v>
       </c>
       <c r="H1174" t="n">
         <v>1515</v>
@@ -34444,7 +34444,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>13.3021030426025</v>
+        <v>13.3021039962769</v>
       </c>
       <c r="H1175" t="n">
         <v>3278</v>
@@ -34473,7 +34473,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>13.3021030426025</v>
+        <v>13.3021039962769</v>
       </c>
       <c r="H1176" t="n">
         <v>7664</v>
@@ -34560,7 +34560,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1179" t="n">
-        <v>13.5417814254761</v>
+        <v>13.5417804718018</v>
       </c>
       <c r="H1179" t="n">
         <v>1996</v>
@@ -34589,7 +34589,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>13.1423196792603</v>
+        <v>13.1423187255859</v>
       </c>
       <c r="H1180" t="n">
         <v>4050</v>
@@ -34618,7 +34618,7 @@
         <v>17</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1181" t="n">
         <v>2247</v>
@@ -34647,7 +34647,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>13.4618892669678</v>
+        <v>13.4618883132935</v>
       </c>
       <c r="H1182" t="n">
         <v>1189</v>
@@ -34676,7 +34676,7 @@
         <v>17</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1183" t="n">
         <v>3404</v>
@@ -34705,7 +34705,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>13.3021030426025</v>
+        <v>13.3021039962769</v>
       </c>
       <c r="H1184" t="n">
         <v>269</v>
@@ -34763,7 +34763,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.4219417572021</v>
+        <v>13.4219408035278</v>
       </c>
       <c r="H1186" t="n">
         <v>1862</v>
@@ -34792,7 +34792,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>13.7415132522583</v>
+        <v>13.7415142059326</v>
       </c>
       <c r="H1187" t="n">
         <v>4016</v>
@@ -34821,7 +34821,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1188" t="n">
-        <v>13.7415132522583</v>
+        <v>13.7415142059326</v>
       </c>
       <c r="H1188" t="n">
         <v>3355</v>
@@ -34850,7 +34850,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>13.7415132522583</v>
+        <v>13.7415142059326</v>
       </c>
       <c r="H1189" t="n">
         <v>3014</v>
@@ -34908,7 +34908,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>13.9012956619263</v>
+        <v>13.9012966156006</v>
       </c>
       <c r="H1191" t="n">
         <v>2561</v>
@@ -34937,7 +34937,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>13.9012956619263</v>
+        <v>13.9012966156006</v>
       </c>
       <c r="H1192" t="n">
         <v>147</v>
@@ -34995,7 +34995,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1194" t="n">
-        <v>13.7415132522583</v>
+        <v>13.7415142059326</v>
       </c>
       <c r="H1194" t="n">
         <v>2530</v>
@@ -35024,7 +35024,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1195" t="n">
-        <v>13.9012956619263</v>
+        <v>13.9012966156006</v>
       </c>
       <c r="H1195" t="n">
         <v>1420</v>
@@ -35053,7 +35053,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.7415132522583</v>
+        <v>13.7415142059326</v>
       </c>
       <c r="H1196" t="n">
         <v>1053</v>
@@ -35082,7 +35082,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1197" t="n">
-        <v>13.4219417572021</v>
+        <v>13.4219408035278</v>
       </c>
       <c r="H1197" t="n">
         <v>2048</v>
@@ -35111,7 +35111,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.4219417572021</v>
+        <v>13.4219408035278</v>
       </c>
       <c r="H1198" t="n">
         <v>1675</v>
@@ -35169,7 +35169,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1200" t="n">
-        <v>13.4219417572021</v>
+        <v>13.4219408035278</v>
       </c>
       <c r="H1200" t="n">
         <v>3610</v>
@@ -35198,7 +35198,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1201" t="n">
-        <v>13.4618892669678</v>
+        <v>13.4618883132935</v>
       </c>
       <c r="H1201" t="n">
         <v>872</v>
@@ -35227,7 +35227,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>13.5417814254761</v>
+        <v>13.5417804718018</v>
       </c>
       <c r="H1202" t="n">
         <v>13581</v>
@@ -35314,7 +35314,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.942587852478</v>
+        <v>12.9425888061523</v>
       </c>
       <c r="H1205" t="n">
         <v>3593</v>
@@ -35343,7 +35343,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.8626937866211</v>
+        <v>12.8626947402954</v>
       </c>
       <c r="H1206" t="n">
         <v>1889</v>
@@ -35430,7 +35430,7 @@
         <v>16.25</v>
       </c>
       <c r="G1209" t="n">
-        <v>12.9825325012207</v>
+        <v>12.982533454895</v>
       </c>
       <c r="H1209" t="n">
         <v>6709</v>
@@ -35459,7 +35459,7 @@
         <v>16.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.1822662353516</v>
+        <v>13.1822652816772</v>
       </c>
       <c r="H1210" t="n">
         <v>2024</v>
@@ -35488,7 +35488,7 @@
         <v>16.5</v>
       </c>
       <c r="G1211" t="n">
-        <v>13.1822662353516</v>
+        <v>13.1822652816772</v>
       </c>
       <c r="H1211" t="n">
         <v>13532</v>
@@ -35546,7 +35546,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1213" t="n">
-        <v>13.821403503418</v>
+        <v>13.8214044570923</v>
       </c>
       <c r="H1213" t="n">
         <v>8038</v>
@@ -35575,7 +35575,7 @@
         <v>17</v>
       </c>
       <c r="G1214" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1214" t="n">
         <v>842</v>
@@ -35662,7 +35662,7 @@
         <v>17</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1217" t="n">
         <v>16448</v>
@@ -35691,7 +35691,7 @@
         <v>17</v>
       </c>
       <c r="G1218" t="n">
-        <v>13.5817270278931</v>
+        <v>13.5817289352417</v>
       </c>
       <c r="H1218" t="n">
         <v>8933</v>
@@ -35807,7 +35807,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1222" t="n">
-        <v>13.1023721694946</v>
+        <v>13.1023712158203</v>
       </c>
       <c r="H1222" t="n">
         <v>766</v>
@@ -36126,7 +36126,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1233" t="n">
-        <v>13.1023721694946</v>
+        <v>13.1023712158203</v>
       </c>
       <c r="H1233" t="n">
         <v>2750</v>
@@ -36184,7 +36184,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>13.4219417572021</v>
+        <v>13.4219408035278</v>
       </c>
       <c r="H1235" t="n">
         <v>10321</v>
@@ -36271,7 +36271,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1238" t="n">
-        <v>14.5404396057129</v>
+        <v>14.5404386520386</v>
       </c>
       <c r="H1238" t="n">
         <v>28813</v>
@@ -36329,7 +36329,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1240" t="n">
-        <v>15.0996837615967</v>
+        <v>15.099681854248</v>
       </c>
       <c r="H1240" t="n">
         <v>14288</v>
@@ -36358,7 +36358,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.7388277053833</v>
+        <v>15.738826751709</v>
       </c>
       <c r="H1241" t="n">
         <v>11666</v>
@@ -36387,7 +36387,7 @@
         <v>19.5</v>
       </c>
       <c r="G1242" t="n">
-        <v>15.5790414810181</v>
+        <v>15.5790395736694</v>
       </c>
       <c r="H1242" t="n">
         <v>9457</v>
@@ -36416,7 +36416,7 @@
         <v>19</v>
       </c>
       <c r="G1243" t="n">
-        <v>15.1795797348022</v>
+        <v>15.179575920105</v>
       </c>
       <c r="H1243" t="n">
         <v>6210</v>
@@ -36503,7 +36503,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1246" t="n">
-        <v>15.0996837615967</v>
+        <v>15.099681854248</v>
       </c>
       <c r="H1246" t="n">
         <v>1183</v>
@@ -36561,7 +36561,7 @@
         <v>18.75</v>
       </c>
       <c r="G1248" t="n">
-        <v>14.9798460006714</v>
+        <v>14.9798469543457</v>
       </c>
       <c r="H1248" t="n">
         <v>2282</v>
@@ -36590,7 +36590,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>15.0597410202026</v>
+        <v>15.059739112854</v>
       </c>
       <c r="H1249" t="n">
         <v>384</v>
@@ -36793,7 +36793,7 @@
         <v>19</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.1795797348022</v>
+        <v>15.179575920105</v>
       </c>
       <c r="H1256" t="n">
         <v>176</v>
@@ -36822,7 +36822,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>15.4192581176758</v>
+        <v>15.4192562103271</v>
       </c>
       <c r="H1257" t="n">
         <v>3510</v>
@@ -36851,7 +36851,7 @@
         <v>19</v>
       </c>
       <c r="G1258" t="n">
-        <v>15.1795797348022</v>
+        <v>15.179575920105</v>
       </c>
       <c r="H1258" t="n">
         <v>1581</v>
@@ -36909,7 +36909,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1260" t="n">
-        <v>15.4192581176758</v>
+        <v>15.4192562103271</v>
       </c>
       <c r="H1260" t="n">
         <v>2564</v>
@@ -36938,7 +36938,7 @@
         <v>19</v>
       </c>
       <c r="G1261" t="n">
-        <v>15.1795797348022</v>
+        <v>15.179575920105</v>
       </c>
       <c r="H1261" t="n">
         <v>5605</v>
@@ -36996,7 +36996,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>15.0996837615967</v>
+        <v>15.099681854248</v>
       </c>
       <c r="H1263" t="n">
         <v>2281</v>
@@ -37054,7 +37054,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>15.4192581176758</v>
+        <v>15.4192562103271</v>
       </c>
       <c r="H1265" t="n">
         <v>18642</v>
@@ -37083,7 +37083,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>14.8999557495117</v>
+        <v>14.8999547958374</v>
       </c>
       <c r="H1266" t="n">
         <v>14379</v>
@@ -37112,7 +37112,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1267" t="n">
-        <v>14.8600072860718</v>
+        <v>14.8600091934204</v>
       </c>
       <c r="H1267" t="n">
         <v>4802</v>
@@ -37141,7 +37141,7 @@
         <v>18.75</v>
       </c>
       <c r="G1268" t="n">
-        <v>14.9798460006714</v>
+        <v>14.9798469543457</v>
       </c>
       <c r="H1268" t="n">
         <v>5006</v>
@@ -37170,7 +37170,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>15.0597410202026</v>
+        <v>15.059739112854</v>
       </c>
       <c r="H1269" t="n">
         <v>437</v>
@@ -37199,7 +37199,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>15.0597410202026</v>
+        <v>15.059739112854</v>
       </c>
       <c r="H1270" t="n">
         <v>493</v>
@@ -37228,7 +37228,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="n">
-        <v>15.1396312713623</v>
+        <v>15.139630317688</v>
       </c>
       <c r="H1271" t="n">
         <v>2264</v>
@@ -37257,7 +37257,7 @@
         <v>19</v>
       </c>
       <c r="G1272" t="n">
-        <v>15.1795797348022</v>
+        <v>15.179575920105</v>
       </c>
       <c r="H1272" t="n">
         <v>4167</v>
@@ -37373,7 +37373,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1276" t="n">
-        <v>17.3366756439209</v>
+        <v>17.3366775512695</v>
       </c>
       <c r="H1276" t="n">
         <v>14827</v>
@@ -37402,7 +37402,7 @@
         <v>21</v>
       </c>
       <c r="G1277" t="n">
-        <v>16.7774276733398</v>
+        <v>16.7774295806885</v>
       </c>
       <c r="H1277" t="n">
         <v>4735</v>
@@ -37547,7 +37547,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1282" t="n">
-        <v>16.1382865905762</v>
+        <v>16.1382884979248</v>
       </c>
       <c r="H1282" t="n">
         <v>7827</v>
@@ -37663,7 +37663,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>16.2181816101074</v>
+        <v>16.2181777954102</v>
       </c>
       <c r="H1286" t="n">
         <v>5146</v>
@@ -37692,7 +37692,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.8986110687256</v>
+        <v>15.898609161377</v>
       </c>
       <c r="H1287" t="n">
         <v>3189</v>
@@ -37837,7 +37837,7 @@
         <v>20.5</v>
       </c>
       <c r="G1292" t="n">
-        <v>16.3779640197754</v>
+        <v>16.377965927124</v>
       </c>
       <c r="H1292" t="n">
         <v>1519</v>
@@ -37866,7 +37866,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1293" t="n">
-        <v>16.8573188781738</v>
+        <v>16.8573226928711</v>
       </c>
       <c r="H1293" t="n">
         <v>19437</v>
@@ -37895,7 +37895,7 @@
         <v>21</v>
       </c>
       <c r="G1294" t="n">
-        <v>16.7774276733398</v>
+        <v>16.7774295806885</v>
       </c>
       <c r="H1294" t="n">
         <v>9574</v>
@@ -38069,7 +38069,7 @@
         <v>22</v>
       </c>
       <c r="G1300" t="n">
-        <v>17.5763511657715</v>
+        <v>17.5763530731201</v>
       </c>
       <c r="H1300" t="n">
         <v>6733</v>
@@ -38098,7 +38098,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.6562461853027</v>
+        <v>17.6562442779541</v>
       </c>
       <c r="H1301" t="n">
         <v>11527</v>
@@ -38127,7 +38127,7 @@
         <v>22</v>
       </c>
       <c r="G1302" t="n">
-        <v>17.5763511657715</v>
+        <v>17.5763530731201</v>
       </c>
       <c r="H1302" t="n">
         <v>8613</v>
@@ -38185,7 +38185,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1304" t="n">
-        <v>16.8573188781738</v>
+        <v>16.8573226928711</v>
       </c>
       <c r="H1304" t="n">
         <v>4715</v>
@@ -38243,7 +38243,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1306" t="n">
-        <v>16.8573188781738</v>
+        <v>16.8573226928711</v>
       </c>
       <c r="H1306" t="n">
         <v>5479</v>
@@ -38272,7 +38272,7 @@
         <v>21</v>
       </c>
       <c r="G1307" t="n">
-        <v>16.7774276733398</v>
+        <v>16.7774295806885</v>
       </c>
       <c r="H1307" t="n">
         <v>5766</v>
@@ -38330,7 +38330,7 @@
         <v>21</v>
       </c>
       <c r="G1309" t="n">
-        <v>16.7774276733398</v>
+        <v>16.7774295806885</v>
       </c>
       <c r="H1309" t="n">
         <v>8017</v>
@@ -38417,7 +38417,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1312" t="n">
-        <v>16.8573188781738</v>
+        <v>16.8573226928711</v>
       </c>
       <c r="H1312" t="n">
         <v>4483</v>
@@ -38533,7 +38533,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>17.7361373901367</v>
+        <v>17.7361392974854</v>
       </c>
       <c r="H1316" t="n">
         <v>22770</v>
@@ -38562,7 +38562,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1317" t="n">
-        <v>17.7361373901367</v>
+        <v>17.7361392974854</v>
       </c>
       <c r="H1317" t="n">
         <v>5131</v>
@@ -38591,7 +38591,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1318" t="n">
-        <v>17.7361373901367</v>
+        <v>17.7361392974854</v>
       </c>
       <c r="H1318" t="n">
         <v>10459</v>
@@ -38620,7 +38620,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1319" t="n">
-        <v>17.816032409668</v>
+        <v>17.8160305023193</v>
       </c>
       <c r="H1319" t="n">
         <v>9556</v>
@@ -38881,7 +38881,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="n">
-        <v>18.375280380249</v>
+        <v>18.3752765655518</v>
       </c>
       <c r="H1328" t="n">
         <v>4296</v>
@@ -39432,7 +39432,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1347" t="n">
-        <v>18.9345264434814</v>
+        <v>18.9345283508301</v>
       </c>
       <c r="H1347" t="n">
         <v>5840</v>
@@ -39461,7 +39461,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>19.0144157409668</v>
+        <v>19.0144176483154</v>
       </c>
       <c r="H1348" t="n">
         <v>2163</v>
@@ -39548,7 +39548,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1351" t="n">
-        <v>19.0144157409668</v>
+        <v>19.0144176483154</v>
       </c>
       <c r="H1351" t="n">
         <v>6654</v>
@@ -39577,7 +39577,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1352" t="n">
-        <v>18.9345264434814</v>
+        <v>18.9345283508301</v>
       </c>
       <c r="H1352" t="n">
         <v>2677</v>
@@ -39664,7 +39664,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="n">
-        <v>18.375280380249</v>
+        <v>18.3752765655518</v>
       </c>
       <c r="H1355" t="n">
         <v>3772</v>
@@ -39693,7 +39693,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="n">
-        <v>18.375280380249</v>
+        <v>18.3752765655518</v>
       </c>
       <c r="H1356" t="n">
         <v>2691</v>
@@ -39722,7 +39722,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.375280380249</v>
+        <v>18.3752765655518</v>
       </c>
       <c r="H1357" t="n">
         <v>3786</v>
@@ -39751,7 +39751,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="n">
-        <v>18.375280380249</v>
+        <v>18.3752765655518</v>
       </c>
       <c r="H1358" t="n">
         <v>4851</v>
@@ -39809,7 +39809,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="n">
-        <v>18.375280380249</v>
+        <v>18.3752765655518</v>
       </c>
       <c r="H1360" t="n">
         <v>5194</v>
@@ -39838,7 +39838,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1361" t="n">
-        <v>18.9345264434814</v>
+        <v>18.9345283508301</v>
       </c>
       <c r="H1361" t="n">
         <v>9125</v>
@@ -39867,7 +39867,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>18.9345264434814</v>
+        <v>18.9345283508301</v>
       </c>
       <c r="H1362" t="n">
         <v>6431</v>
@@ -39983,7 +39983,7 @@
         <v>23</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.0790157318115</v>
+        <v>19.0790138244629</v>
       </c>
       <c r="H1366" t="n">
         <v>4785</v>
@@ -40070,7 +40070,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>18.9960594177246</v>
+        <v>18.996057510376</v>
       </c>
       <c r="H1369" t="n">
         <v>3680</v>
@@ -40853,7 +40853,7 @@
         <v>23</v>
       </c>
       <c r="G1396" t="n">
-        <v>19.0790157318115</v>
+        <v>19.0790138244629</v>
       </c>
       <c r="H1396" t="n">
         <v>9212</v>
@@ -40940,7 +40940,7 @@
         <v>23</v>
       </c>
       <c r="G1399" t="n">
-        <v>19.0790157318115</v>
+        <v>19.0790138244629</v>
       </c>
       <c r="H1399" t="n">
         <v>7735</v>
@@ -40969,7 +40969,7 @@
         <v>23</v>
       </c>
       <c r="G1400" t="n">
-        <v>19.0790157318115</v>
+        <v>19.0790138244629</v>
       </c>
       <c r="H1400" t="n">
         <v>755</v>
@@ -40998,7 +40998,7 @@
         <v>23</v>
       </c>
       <c r="G1401" t="n">
-        <v>19.0790157318115</v>
+        <v>19.0790138244629</v>
       </c>
       <c r="H1401" t="n">
         <v>5090</v>
@@ -41085,7 +41085,7 @@
         <v>23</v>
       </c>
       <c r="G1404" t="n">
-        <v>19.0790157318115</v>
+        <v>19.0790138244629</v>
       </c>
       <c r="H1404" t="n">
         <v>678</v>
@@ -41114,7 +41114,7 @@
         <v>23</v>
       </c>
       <c r="G1405" t="n">
-        <v>19.0790157318115</v>
+        <v>19.0790138244629</v>
       </c>
       <c r="H1405" t="n">
         <v>0</v>
@@ -41143,7 +41143,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1406" t="n">
-        <v>18.9960594177246</v>
+        <v>18.996057510376</v>
       </c>
       <c r="H1406" t="n">
         <v>2642</v>
@@ -41201,7 +41201,7 @@
         <v>22.5</v>
       </c>
       <c r="G1408" t="n">
-        <v>18.6642532348633</v>
+        <v>18.6642513275146</v>
       </c>
       <c r="H1408" t="n">
         <v>3012</v>
@@ -41259,7 +41259,7 @@
         <v>22.5</v>
       </c>
       <c r="G1410" t="n">
-        <v>18.6642532348633</v>
+        <v>18.6642513275146</v>
       </c>
       <c r="H1410" t="n">
         <v>8181</v>
@@ -41288,7 +41288,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>18.9960594177246</v>
+        <v>18.996057510376</v>
       </c>
       <c r="H1411" t="n">
         <v>1449</v>
@@ -41346,7 +41346,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>18.9960594177246</v>
+        <v>18.996057510376</v>
       </c>
       <c r="H1413" t="n">
         <v>906</v>
@@ -41520,7 +41520,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1419" t="n">
-        <v>19.9914875030518</v>
+        <v>19.9914855957031</v>
       </c>
       <c r="H1419" t="n">
         <v>7814</v>
@@ -41549,7 +41549,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1420" t="n">
-        <v>19.9914875030518</v>
+        <v>19.9914855957031</v>
       </c>
       <c r="H1420" t="n">
         <v>2727</v>
@@ -41897,7 +41897,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>19.9914875030518</v>
+        <v>19.9914855957031</v>
       </c>
       <c r="H1432" t="n">
         <v>6733</v>
@@ -42042,7 +42042,7 @@
         <v>26.5</v>
       </c>
       <c r="G1437" t="n">
-        <v>21.9823417663574</v>
+        <v>21.9823398590088</v>
       </c>
       <c r="H1437" t="n">
         <v>8469</v>
@@ -42158,7 +42158,7 @@
         <v>26.5</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.9823417663574</v>
+        <v>21.9823398590088</v>
       </c>
       <c r="H1441" t="n">
         <v>2176</v>
@@ -42187,7 +42187,7 @@
         <v>26.5</v>
       </c>
       <c r="G1442" t="n">
-        <v>21.9823417663574</v>
+        <v>21.9823398590088</v>
       </c>
       <c r="H1442" t="n">
         <v>6836</v>
@@ -42245,7 +42245,7 @@
         <v>26.5</v>
       </c>
       <c r="G1444" t="n">
-        <v>21.9823417663574</v>
+        <v>21.9823398590088</v>
       </c>
       <c r="H1444" t="n">
         <v>15562</v>
@@ -42274,7 +42274,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>22.1482486724854</v>
+        <v>22.1482467651367</v>
       </c>
       <c r="H1445" t="n">
         <v>8127</v>
@@ -42303,7 +42303,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1446" t="n">
-        <v>22.3141479492188</v>
+        <v>22.3141498565674</v>
       </c>
       <c r="H1446" t="n">
         <v>14954</v>
@@ -42361,7 +42361,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1448" t="n">
-        <v>22.3141479492188</v>
+        <v>22.3141498565674</v>
       </c>
       <c r="H1448" t="n">
         <v>6122</v>
@@ -42448,7 +42448,7 @@
         <v>27.5</v>
       </c>
       <c r="G1451" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1451" t="n">
         <v>1512</v>
@@ -42506,7 +42506,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>22.8948173522949</v>
+        <v>22.8948154449463</v>
       </c>
       <c r="H1453" t="n">
         <v>1798</v>
@@ -42535,7 +42535,7 @@
         <v>27.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1454" t="n">
         <v>4424</v>
@@ -42564,7 +42564,7 @@
         <v>27.5</v>
       </c>
       <c r="G1455" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1455" t="n">
         <v>4772</v>
@@ -42738,7 +42738,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1461" t="n">
-        <v>22.6459560394287</v>
+        <v>22.6459579467773</v>
       </c>
       <c r="H1461" t="n">
         <v>1398</v>
@@ -42767,7 +42767,7 @@
         <v>27.5</v>
       </c>
       <c r="G1462" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1462" t="n">
         <v>1430</v>
@@ -42796,7 +42796,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1463" t="n">
-        <v>22.7289085388184</v>
+        <v>22.728910446167</v>
       </c>
       <c r="H1463" t="n">
         <v>2348</v>
@@ -42825,7 +42825,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1464" t="n">
-        <v>22.7289085388184</v>
+        <v>22.728910446167</v>
       </c>
       <c r="H1464" t="n">
         <v>919</v>
@@ -42854,7 +42854,7 @@
         <v>26.5</v>
       </c>
       <c r="G1465" t="n">
-        <v>21.9823417663574</v>
+        <v>21.9823398590088</v>
       </c>
       <c r="H1465" t="n">
         <v>7725</v>
@@ -42970,7 +42970,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1469" t="n">
-        <v>22.8948173522949</v>
+        <v>22.8948154449463</v>
       </c>
       <c r="H1469" t="n">
         <v>2091</v>
@@ -42999,7 +42999,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1470" t="n">
-        <v>22.1482486724854</v>
+        <v>22.1482467651367</v>
       </c>
       <c r="H1470" t="n">
         <v>1182</v>
@@ -43028,7 +43028,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1471" t="n">
-        <v>22.1482486724854</v>
+        <v>22.1482467651367</v>
       </c>
       <c r="H1471" t="n">
         <v>2036</v>
@@ -43057,7 +43057,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1472" t="n">
-        <v>22.3141479492188</v>
+        <v>22.3141498565674</v>
       </c>
       <c r="H1472" t="n">
         <v>1174</v>
@@ -43115,7 +43115,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>22.3141479492188</v>
+        <v>22.3141498565674</v>
       </c>
       <c r="H1474" t="n">
         <v>1564</v>
@@ -43144,7 +43144,7 @@
         <v>27.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1475" t="n">
         <v>3209</v>
@@ -43202,7 +43202,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1477" t="n">
-        <v>22.7289085388184</v>
+        <v>22.728910446167</v>
       </c>
       <c r="H1477" t="n">
         <v>2190</v>
@@ -43231,7 +43231,7 @@
         <v>27.5</v>
       </c>
       <c r="G1478" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1478" t="n">
         <v>2906</v>
@@ -43376,7 +43376,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1483" t="n">
-        <v>22.3141479492188</v>
+        <v>22.3141498565674</v>
       </c>
       <c r="H1483" t="n">
         <v>1195</v>
@@ -43405,7 +43405,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>22.6459560394287</v>
+        <v>22.6459579467773</v>
       </c>
       <c r="H1484" t="n">
         <v>914</v>
@@ -43434,7 +43434,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1485" t="n">
-        <v>22.8948173522949</v>
+        <v>22.8948154449463</v>
       </c>
       <c r="H1485" t="n">
         <v>6349</v>
@@ -43463,7 +43463,7 @@
         <v>27.5</v>
       </c>
       <c r="G1486" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1486" t="n">
         <v>1784</v>
@@ -43492,7 +43492,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>22.8948173522949</v>
+        <v>22.8948154449463</v>
       </c>
       <c r="H1487" t="n">
         <v>912</v>
@@ -43521,7 +43521,7 @@
         <v>27.5</v>
       </c>
       <c r="G1488" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1488" t="n">
         <v>5177</v>
@@ -43579,7 +43579,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>22.8948173522949</v>
+        <v>22.8948154449463</v>
       </c>
       <c r="H1490" t="n">
         <v>3841</v>
@@ -43724,7 +43724,7 @@
         <v>28.5</v>
       </c>
       <c r="G1495" t="n">
-        <v>23.6413841247559</v>
+        <v>23.6413860321045</v>
       </c>
       <c r="H1495" t="n">
         <v>3136</v>
@@ -43782,7 +43782,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1497" t="n">
-        <v>24.3879547119141</v>
+        <v>24.3879566192627</v>
       </c>
       <c r="H1497" t="n">
         <v>2430</v>
@@ -43898,7 +43898,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>22.6459560394287</v>
+        <v>22.6459579467773</v>
       </c>
       <c r="H1501" t="n">
         <v>24251</v>
@@ -43927,7 +43927,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>22.6459560394287</v>
+        <v>22.6459579467773</v>
       </c>
       <c r="H1502" t="n">
         <v>6826</v>
@@ -43956,7 +43956,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1503" t="n">
-        <v>22.6459560394287</v>
+        <v>22.6459579467773</v>
       </c>
       <c r="H1503" t="n">
         <v>4990</v>
@@ -44014,7 +44014,7 @@
         <v>29</v>
       </c>
       <c r="G1505" t="n">
-        <v>24.0561466217041</v>
+        <v>24.0561485290527</v>
       </c>
       <c r="H1505" t="n">
         <v>10181</v>
@@ -44072,7 +44072,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1507" t="n">
-        <v>24.3879547119141</v>
+        <v>24.3879566192627</v>
       </c>
       <c r="H1507" t="n">
         <v>3371</v>
@@ -44101,7 +44101,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1508" t="n">
-        <v>23.9731960296631</v>
+        <v>23.9731941223145</v>
       </c>
       <c r="H1508" t="n">
         <v>8075</v>
@@ -44159,7 +44159,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1510" t="n">
-        <v>24.5538578033447</v>
+        <v>24.5538597106934</v>
       </c>
       <c r="H1510" t="n">
         <v>8633</v>
@@ -44217,7 +44217,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1512" t="n">
-        <v>24.5538578033447</v>
+        <v>24.5538597106934</v>
       </c>
       <c r="H1512" t="n">
         <v>4317</v>
@@ -44246,7 +44246,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1513" t="n">
-        <v>24.8027172088623</v>
+        <v>24.8027191162109</v>
       </c>
       <c r="H1513" t="n">
         <v>3788</v>
@@ -44391,7 +44391,7 @@
         <v>31</v>
       </c>
       <c r="G1518" t="n">
-        <v>25.7151889801025</v>
+        <v>25.7151908874512</v>
       </c>
       <c r="H1518" t="n">
         <v>6786</v>
@@ -44420,7 +44420,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>25.8810958862305</v>
+        <v>25.8810977935791</v>
       </c>
       <c r="H1519" t="n">
         <v>9189</v>
@@ -44449,7 +44449,7 @@
         <v>31</v>
       </c>
       <c r="G1520" t="n">
-        <v>25.7151889801025</v>
+        <v>25.7151908874512</v>
       </c>
       <c r="H1520" t="n">
         <v>1541</v>
@@ -44478,7 +44478,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>25.8810958862305</v>
+        <v>25.8810977935791</v>
       </c>
       <c r="H1521" t="n">
         <v>7312</v>
@@ -44536,7 +44536,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1523" t="n">
-        <v>27.2912845611572</v>
+        <v>27.2912826538086</v>
       </c>
       <c r="H1523" t="n">
         <v>10476</v>
@@ -44565,7 +44565,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1524" t="n">
-        <v>28.9503288269043</v>
+        <v>28.9503326416016</v>
       </c>
       <c r="H1524" t="n">
         <v>14812</v>
@@ -44594,7 +44594,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1525" t="n">
-        <v>28.7014675140381</v>
+        <v>28.7014694213867</v>
       </c>
       <c r="H1525" t="n">
         <v>10541</v>
@@ -44623,7 +44623,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>28.3696632385254</v>
+        <v>28.3696613311768</v>
       </c>
       <c r="H1526" t="n">
         <v>10724</v>
@@ -44710,7 +44710,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1529" t="n">
-        <v>28.3696632385254</v>
+        <v>28.3696613311768</v>
       </c>
       <c r="H1529" t="n">
         <v>18647</v>
@@ -44739,7 +44739,7 @@
         <v>34.5</v>
       </c>
       <c r="G1530" t="n">
-        <v>28.6185207366943</v>
+        <v>28.6185188293457</v>
       </c>
       <c r="H1530" t="n">
         <v>3378</v>
@@ -44768,7 +44768,7 @@
         <v>33</v>
       </c>
       <c r="G1531" t="n">
-        <v>27.3742370605469</v>
+        <v>27.3742351531982</v>
       </c>
       <c r="H1531" t="n">
         <v>3411</v>
@@ -44826,7 +44826,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1533" t="n">
-        <v>28.3696632385254</v>
+        <v>28.3696613311768</v>
       </c>
       <c r="H1533" t="n">
         <v>12796</v>
@@ -44913,7 +44913,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1536" t="n">
-        <v>26.876522064209</v>
+        <v>26.8765201568604</v>
       </c>
       <c r="H1536" t="n">
         <v>8272</v>
@@ -45000,7 +45000,7 @@
         <v>33</v>
       </c>
       <c r="G1539" t="n">
-        <v>27.3742370605469</v>
+        <v>27.3742351531982</v>
       </c>
       <c r="H1539" t="n">
         <v>1459</v>
@@ -45029,7 +45029,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1540" t="n">
-        <v>27.5401401519775</v>
+        <v>27.5401382446289</v>
       </c>
       <c r="H1540" t="n">
         <v>1866</v>
@@ -45058,7 +45058,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1541" t="n">
-        <v>26.7106170654297</v>
+        <v>26.7106189727783</v>
       </c>
       <c r="H1541" t="n">
         <v>5085</v>
@@ -45087,7 +45087,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>25.1345252990723</v>
+        <v>25.1345272064209</v>
       </c>
       <c r="H1542" t="n">
         <v>17511</v>
@@ -45116,7 +45116,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1543" t="n">
-        <v>24.8027172088623</v>
+        <v>24.8027191162109</v>
       </c>
       <c r="H1543" t="n">
         <v>4710</v>
@@ -45174,7 +45174,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1545" t="n">
-        <v>25.1345252990723</v>
+        <v>25.1345272064209</v>
       </c>
       <c r="H1545" t="n">
         <v>1228</v>
@@ -45203,7 +45203,7 @@
         <v>30.5</v>
       </c>
       <c r="G1546" t="n">
-        <v>25.3004283905029</v>
+        <v>25.3004302978516</v>
       </c>
       <c r="H1546" t="n">
         <v>2141</v>
@@ -45232,7 +45232,7 @@
         <v>30.5</v>
       </c>
       <c r="G1547" t="n">
-        <v>25.3004283905029</v>
+        <v>25.3004302978516</v>
       </c>
       <c r="H1547" t="n">
         <v>4560</v>
@@ -45261,7 +45261,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>25.7981433868408</v>
+        <v>25.7981452941895</v>
       </c>
       <c r="H1548" t="n">
         <v>5190</v>
@@ -45319,7 +45319,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1550" t="n">
-        <v>25.7981433868408</v>
+        <v>25.7981452941895</v>
       </c>
       <c r="H1550" t="n">
         <v>1719</v>
@@ -45348,7 +45348,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1551" t="n">
-        <v>25.1345252990723</v>
+        <v>25.1345272064209</v>
       </c>
       <c r="H1551" t="n">
         <v>4760</v>
@@ -45377,7 +45377,7 @@
         <v>30.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>25.3004283905029</v>
+        <v>25.3004302978516</v>
       </c>
       <c r="H1552" t="n">
         <v>3976</v>
@@ -45522,7 +45522,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1557" t="n">
-        <v>24.5538578033447</v>
+        <v>24.5538597106934</v>
       </c>
       <c r="H1557" t="n">
         <v>14346</v>
@@ -45580,7 +45580,7 @@
         <v>31</v>
       </c>
       <c r="G1559" t="n">
-        <v>25.7151889801025</v>
+        <v>25.7151908874512</v>
       </c>
       <c r="H1559" t="n">
         <v>4090</v>
@@ -45667,7 +45667,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1562" t="n">
-        <v>25.8810958862305</v>
+        <v>25.8810977935791</v>
       </c>
       <c r="H1562" t="n">
         <v>4808</v>
@@ -45696,7 +45696,7 @@
         <v>30.5</v>
       </c>
       <c r="G1563" t="n">
-        <v>25.3004283905029</v>
+        <v>25.3004302978516</v>
       </c>
       <c r="H1563" t="n">
         <v>3507</v>
@@ -45754,7 +45754,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1565" t="n">
-        <v>25.1345252990723</v>
+        <v>25.1345272064209</v>
       </c>
       <c r="H1565" t="n">
         <v>5983</v>
@@ -45783,7 +45783,7 @@
         <v>30.5</v>
       </c>
       <c r="G1566" t="n">
-        <v>25.3004283905029</v>
+        <v>25.3004302978516</v>
       </c>
       <c r="H1566" t="n">
         <v>6198</v>
@@ -45812,7 +45812,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1567" t="n">
-        <v>24.8027172088623</v>
+        <v>24.8027191162109</v>
       </c>
       <c r="H1567" t="n">
         <v>7487</v>
@@ -46015,7 +46015,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1574" t="n">
-        <v>22.7289085388184</v>
+        <v>22.728910446167</v>
       </c>
       <c r="H1574" t="n">
         <v>9986</v>
@@ -46102,7 +46102,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>22.4800567626953</v>
+        <v>22.4800548553467</v>
       </c>
       <c r="H1577" t="n">
         <v>19584</v>
@@ -46189,7 +46189,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1580" t="n">
-        <v>22.1482486724854</v>
+        <v>22.1482467651367</v>
       </c>
       <c r="H1580" t="n">
         <v>12365</v>
@@ -46218,7 +46218,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>22.1482486724854</v>
+        <v>22.1482467651367</v>
       </c>
       <c r="H1581" t="n">
         <v>7775</v>
@@ -46276,7 +46276,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1583" t="n">
-        <v>23.9731960296631</v>
+        <v>23.9731941223145</v>
       </c>
       <c r="H1583" t="n">
         <v>6474</v>
@@ -46334,7 +46334,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1585" t="n">
-        <v>23.8072891235352</v>
+        <v>23.8072910308838</v>
       </c>
       <c r="H1585" t="n">
         <v>10040</v>
@@ -46392,7 +46392,7 @@
         <v>28.5</v>
       </c>
       <c r="G1587" t="n">
-        <v>23.6413841247559</v>
+        <v>23.6413860321045</v>
       </c>
       <c r="H1587" t="n">
         <v>5972</v>
@@ -46740,7 +46740,7 @@
         <v>27.5</v>
       </c>
       <c r="G1599" t="n">
-        <v>22.8118629455566</v>
+        <v>22.8118648529053</v>
       </c>
       <c r="H1599" t="n">
         <v>2162</v>
@@ -46769,7 +46769,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1600" t="n">
-        <v>22.8948173522949</v>
+        <v>22.8948154449463</v>
       </c>
       <c r="H1600" t="n">
         <v>6517</v>
@@ -46972,7 +46972,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1607" t="n">
-        <v>22.4800567626953</v>
+        <v>22.4800548553467</v>
       </c>
       <c r="H1607" t="n">
         <v>6771</v>
@@ -47001,7 +47001,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1608" t="n">
-        <v>22.7289085388184</v>
+        <v>22.728910446167</v>
       </c>
       <c r="H1608" t="n">
         <v>1606</v>
@@ -47030,7 +47030,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1609" t="n">
-        <v>22.7289085388184</v>
+        <v>22.728910446167</v>
       </c>
       <c r="H1609" t="n">
         <v>969</v>
@@ -47233,7 +47233,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1616" t="n">
-        <v>22.2523899078369</v>
+        <v>22.2523918151855</v>
       </c>
       <c r="H1616" t="n">
         <v>5882</v>
@@ -47291,7 +47291,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>22.2523899078369</v>
+        <v>22.2523918151855</v>
       </c>
       <c r="H1618" t="n">
         <v>3604</v>
@@ -47378,7 +47378,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>23.2048244476318</v>
+        <v>23.2048263549805</v>
       </c>
       <c r="H1621" t="n">
         <v>1377</v>
@@ -47697,7 +47697,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1632" t="n">
-        <v>24.7633571624756</v>
+        <v>24.7633590698242</v>
       </c>
       <c r="H1632" t="n">
         <v>4447</v>
@@ -47842,7 +47842,7 @@
         <v>27.5</v>
       </c>
       <c r="G1637" t="n">
-        <v>23.8109226226807</v>
+        <v>23.8109245300293</v>
       </c>
       <c r="H1637" t="n">
         <v>325</v>
@@ -47929,7 +47929,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1640" t="n">
-        <v>21.8194637298584</v>
+        <v>21.8194618225098</v>
       </c>
       <c r="H1640" t="n">
         <v>5650</v>
@@ -47987,7 +47987,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1642" t="n">
-        <v>21.3865394592285</v>
+        <v>21.3865375518799</v>
       </c>
       <c r="H1642" t="n">
         <v>5991</v>
@@ -48277,7 +48277,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1652" t="n">
-        <v>20.6938533782959</v>
+        <v>20.6938552856445</v>
       </c>
       <c r="H1652" t="n">
         <v>2096</v>
@@ -48393,7 +48393,7 @@
         <v>27.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>23.8109226226807</v>
+        <v>23.8109245300293</v>
       </c>
       <c r="H1656" t="n">
         <v>23548</v>
@@ -48451,7 +48451,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1658" t="n">
-        <v>24.1572608947754</v>
+        <v>24.157262802124</v>
       </c>
       <c r="H1658" t="n">
         <v>5117</v>
@@ -48480,7 +48480,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1659" t="n">
-        <v>24.1572608947754</v>
+        <v>24.157262802124</v>
       </c>
       <c r="H1659" t="n">
         <v>2822</v>
@@ -48509,7 +48509,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1660" t="n">
-        <v>24.1572608947754</v>
+        <v>24.157262802124</v>
       </c>
       <c r="H1660" t="n">
         <v>903</v>
@@ -48567,7 +48567,7 @@
         <v>27.5</v>
       </c>
       <c r="G1662" t="n">
-        <v>23.8109226226807</v>
+        <v>23.8109245300293</v>
       </c>
       <c r="H1662" t="n">
         <v>6647</v>
@@ -48654,7 +48654,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1665" t="n">
-        <v>23.2048244476318</v>
+        <v>23.2048263549805</v>
       </c>
       <c r="H1665" t="n">
         <v>6039</v>
@@ -48828,7 +48828,7 @@
         <v>27.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>23.8109226226807</v>
+        <v>23.8109245300293</v>
       </c>
       <c r="H1671" t="n">
         <v>8330</v>
@@ -49089,7 +49089,7 @@
         <v>27.5</v>
       </c>
       <c r="G1680" t="n">
-        <v>23.8109226226807</v>
+        <v>23.8109245300293</v>
       </c>
       <c r="H1680" t="n">
         <v>581</v>
@@ -49408,7 +49408,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1691" t="n">
-        <v>23.2048244476318</v>
+        <v>23.2048263549805</v>
       </c>
       <c r="H1691" t="n">
         <v>2077</v>
@@ -49640,7 +49640,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1699" t="n">
-        <v>22.2523899078369</v>
+        <v>22.2523918151855</v>
       </c>
       <c r="H1699" t="n">
         <v>1168</v>
@@ -49959,7 +49959,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1710" t="n">
-        <v>21.3865394592285</v>
+        <v>21.3865375518799</v>
       </c>
       <c r="H1710" t="n">
         <v>4157</v>
@@ -50017,7 +50017,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1712" t="n">
-        <v>21.3865394592285</v>
+        <v>21.3865375518799</v>
       </c>
       <c r="H1712" t="n">
         <v>2035</v>
@@ -50133,7 +50133,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1716" t="n">
-        <v>21.3865394592285</v>
+        <v>21.3865375518799</v>
       </c>
       <c r="H1716" t="n">
         <v>3836</v>
@@ -50423,7 +50423,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1726" t="n">
-        <v>20.8670291900635</v>
+        <v>20.8670272827148</v>
       </c>
       <c r="H1726" t="n">
         <v>604</v>
@@ -50481,7 +50481,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1728" t="n">
-        <v>21.3865394592285</v>
+        <v>21.3865375518799</v>
       </c>
       <c r="H1728" t="n">
         <v>843</v>
@@ -50568,7 +50568,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1731" t="n">
-        <v>22.2523899078369</v>
+        <v>22.2523918151855</v>
       </c>
       <c r="H1731" t="n">
         <v>664</v>
@@ -50597,7 +50597,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1732" t="n">
-        <v>21.3865394592285</v>
+        <v>21.3865375518799</v>
       </c>
       <c r="H1732" t="n">
         <v>2470</v>
@@ -50887,7 +50887,7 @@
         <v>27.5</v>
       </c>
       <c r="G1742" t="n">
-        <v>23.8109226226807</v>
+        <v>23.8109245300293</v>
       </c>
       <c r="H1742" t="n">
         <v>3383</v>
@@ -50974,7 +50974,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1745" t="n">
-        <v>23.2048244476318</v>
+        <v>23.2048263549805</v>
       </c>
       <c r="H1745" t="n">
         <v>1027</v>
@@ -51032,7 +51032,7 @@
         <v>27.5</v>
       </c>
       <c r="G1747" t="n">
-        <v>23.8109226226807</v>
+        <v>23.8109245300293</v>
       </c>
       <c r="H1747" t="n">
         <v>1797</v>
@@ -51264,7 +51264,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1755" t="n">
-        <v>24.1572608947754</v>
+        <v>24.157262802124</v>
       </c>
       <c r="H1755" t="n">
         <v>1052</v>
@@ -51322,7 +51322,7 @@
         <v>27.5</v>
       </c>
       <c r="G1757" t="n">
-        <v>23.8109226226807</v>
+        <v>23.8109245300293</v>
       </c>
       <c r="H1757" t="n">
         <v>2924</v>
@@ -51728,7 +51728,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1771" t="n">
-        <v>25.3694553375244</v>
+        <v>25.369457244873</v>
       </c>
       <c r="H1771" t="n">
         <v>2995</v>
@@ -51815,7 +51815,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1774" t="n">
-        <v>25.3694553375244</v>
+        <v>25.369457244873</v>
       </c>
       <c r="H1774" t="n">
         <v>3848</v>
@@ -51873,7 +51873,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1776" t="n">
-        <v>26.6682319641113</v>
+        <v>26.66823387146</v>
       </c>
       <c r="H1776" t="n">
         <v>7234</v>
@@ -51931,7 +51931,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1778" t="n">
-        <v>26.9279899597168</v>
+        <v>26.9279918670654</v>
       </c>
       <c r="H1778" t="n">
         <v>16545</v>
@@ -51960,7 +51960,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1779" t="n">
-        <v>26.6682319641113</v>
+        <v>26.66823387146</v>
       </c>
       <c r="H1779" t="n">
         <v>6565</v>
@@ -52192,7 +52192,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1787" t="n">
-        <v>26.321891784668</v>
+        <v>26.3218936920166</v>
       </c>
       <c r="H1787" t="n">
         <v>660</v>
@@ -52221,7 +52221,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1788" t="n">
-        <v>26.6682319641113</v>
+        <v>26.66823387146</v>
       </c>
       <c r="H1788" t="n">
         <v>6621</v>
@@ -52250,7 +52250,7 @@
         <v>30.5</v>
       </c>
       <c r="G1789" t="n">
-        <v>26.4084777832031</v>
+        <v>26.4084796905518</v>
       </c>
       <c r="H1789" t="n">
         <v>1507</v>
@@ -52308,7 +52308,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1791" t="n">
-        <v>26.321891784668</v>
+        <v>26.3218936920166</v>
       </c>
       <c r="H1791" t="n">
         <v>2211</v>
@@ -52337,7 +52337,7 @@
         <v>30.5</v>
       </c>
       <c r="G1792" t="n">
-        <v>26.4084777832031</v>
+        <v>26.4084796905518</v>
       </c>
       <c r="H1792" t="n">
         <v>1377</v>
@@ -52424,7 +52424,7 @@
         <v>31</v>
       </c>
       <c r="G1795" t="n">
-        <v>26.841402053833</v>
+        <v>26.8414039611816</v>
       </c>
       <c r="H1795" t="n">
         <v>2139</v>
@@ -52482,7 +52482,7 @@
         <v>31</v>
       </c>
       <c r="G1797" t="n">
-        <v>26.841402053833</v>
+        <v>26.8414039611816</v>
       </c>
       <c r="H1797" t="n">
         <v>4421</v>
@@ -52511,7 +52511,7 @@
         <v>31</v>
       </c>
       <c r="G1798" t="n">
-        <v>26.841402053833</v>
+        <v>26.8414039611816</v>
       </c>
       <c r="H1798" t="n">
         <v>1383</v>
@@ -52569,7 +52569,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1800" t="n">
-        <v>26.6682319641113</v>
+        <v>26.66823387146</v>
       </c>
       <c r="H1800" t="n">
         <v>413</v>
@@ -52598,7 +52598,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1801" t="n">
-        <v>26.321891784668</v>
+        <v>26.3218936920166</v>
       </c>
       <c r="H1801" t="n">
         <v>3475</v>
@@ -52627,7 +52627,7 @@
         <v>31</v>
       </c>
       <c r="G1802" t="n">
-        <v>26.841402053833</v>
+        <v>26.8414039611816</v>
       </c>
       <c r="H1802" t="n">
         <v>2623</v>
@@ -52656,7 +52656,7 @@
         <v>30.5</v>
       </c>
       <c r="G1803" t="n">
-        <v>26.4084777832031</v>
+        <v>26.4084796905518</v>
       </c>
       <c r="H1803" t="n">
         <v>511</v>
@@ -52743,7 +52743,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>25.8889656066895</v>
+        <v>25.8889675140381</v>
       </c>
       <c r="H1806" t="n">
         <v>1674</v>
@@ -52801,7 +52801,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1808" t="n">
-        <v>25.3694553375244</v>
+        <v>25.369457244873</v>
       </c>
       <c r="H1808" t="n">
         <v>1907</v>
@@ -53323,7 +53323,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1826" t="n">
-        <v>25.3694553375244</v>
+        <v>25.369457244873</v>
       </c>
       <c r="H1826" t="n">
         <v>3490</v>
@@ -53410,7 +53410,7 @@
         <v>30.5</v>
       </c>
       <c r="G1829" t="n">
-        <v>26.4084777832031</v>
+        <v>26.4084796905518</v>
       </c>
       <c r="H1829" t="n">
         <v>6449</v>
@@ -53468,7 +53468,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1831" t="n">
-        <v>25.8889656066895</v>
+        <v>25.8889675140381</v>
       </c>
       <c r="H1831" t="n">
         <v>3960</v>
@@ -53671,7 +53671,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1838" t="n">
-        <v>25.7157955169678</v>
+        <v>25.7157974243164</v>
       </c>
       <c r="H1838" t="n">
         <v>791</v>
@@ -53700,7 +53700,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1839" t="n">
-        <v>26.6682319641113</v>
+        <v>26.66823387146</v>
       </c>
       <c r="H1839" t="n">
         <v>10612</v>
@@ -53787,7 +53787,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1842" t="n">
-        <v>26.6682319641113</v>
+        <v>26.66823387146</v>
       </c>
       <c r="H1842" t="n">
         <v>4296</v>
@@ -53932,7 +53932,7 @@
         <v>30.5</v>
       </c>
       <c r="G1847" t="n">
-        <v>26.4084777832031</v>
+        <v>26.4084796905518</v>
       </c>
       <c r="H1847" t="n">
         <v>4626</v>
@@ -53961,7 +53961,7 @@
         <v>30.5</v>
       </c>
       <c r="G1848" t="n">
-        <v>26.4084777832031</v>
+        <v>26.4084796905518</v>
       </c>
       <c r="H1848" t="n">
         <v>11815</v>
@@ -54077,7 +54077,7 @@
         <v>30.5</v>
       </c>
       <c r="G1852" t="n">
-        <v>26.4084777832031</v>
+        <v>26.4084796905518</v>
       </c>
       <c r="H1852" t="n">
         <v>3496</v>
@@ -54135,7 +54135,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1854" t="n">
-        <v>25.7157955169678</v>
+        <v>25.7157974243164</v>
       </c>
       <c r="H1854" t="n">
         <v>2759</v>
@@ -54164,7 +54164,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1855" t="n">
-        <v>26.321891784668</v>
+        <v>26.3218936920166</v>
       </c>
       <c r="H1855" t="n">
         <v>2481</v>
@@ -54193,7 +54193,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1856" t="n">
-        <v>26.321891784668</v>
+        <v>26.3218936920166</v>
       </c>
       <c r="H1856" t="n">
         <v>4494</v>
@@ -54222,7 +54222,7 @@
         <v>30.5</v>
       </c>
       <c r="G1857" t="n">
-        <v>26.4084777832031</v>
+        <v>26.4084796905518</v>
       </c>
       <c r="H1857" t="n">
         <v>4085</v>
@@ -54309,7 +54309,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1860" t="n">
-        <v>25.8889656066895</v>
+        <v>25.8889675140381</v>
       </c>
       <c r="H1860" t="n">
         <v>1779</v>
@@ -54367,7 +54367,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1862" t="n">
-        <v>25.8889656066895</v>
+        <v>25.8889675140381</v>
       </c>
       <c r="H1862" t="n">
         <v>4931</v>
@@ -54483,7 +54483,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1866" t="n">
-        <v>26.9279899597168</v>
+        <v>26.9279918670654</v>
       </c>
       <c r="H1866" t="n">
         <v>9770</v>
@@ -54512,7 +54512,7 @@
         <v>31.5</v>
       </c>
       <c r="G1867" t="n">
-        <v>27.2743282318115</v>
+        <v>27.2743301391602</v>
       </c>
       <c r="H1867" t="n">
         <v>10798</v>
@@ -54541,7 +54541,7 @@
         <v>31.5</v>
       </c>
       <c r="G1868" t="n">
-        <v>27.2743282318115</v>
+        <v>27.2743301391602</v>
       </c>
       <c r="H1868" t="n">
         <v>39557</v>
@@ -54570,7 +54570,7 @@
         <v>31.5</v>
       </c>
       <c r="G1869" t="n">
-        <v>27.2743282318115</v>
+        <v>27.2743301391602</v>
       </c>
       <c r="H1869" t="n">
         <v>17498</v>
@@ -80125,6 +80125,35 @@
         <v>8851</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>77.1999969482422</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>79.0999984741211</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>77.0999984741211</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>78.5999984741211</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>78.5999984741211</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>7573</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>
